--- a/datosSesiones.xlsx
+++ b/datosSesiones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\hlocal\C_TFG\Datos\Mision Colombia-20260209T150018Z-3-001\jsonToCsv_TFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A78123C3-E771-4EA1-B8D9-3D92BE62AE36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{578773CA-B47C-4DE8-A49E-5714DF734B57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="275">
   <si>
     <t>ID</t>
   </si>
@@ -98,102 +98,201 @@
     <t>Num errores por tiempo excedido</t>
   </si>
   <si>
+    <t>% Aciertos</t>
+  </si>
+  <si>
+    <t>% Mal</t>
+  </si>
+  <si>
     <t>15:04:04.517</t>
   </si>
   <si>
     <t>15:20:46.000</t>
   </si>
   <si>
+    <t>78.57142857142857</t>
+  </si>
+  <si>
+    <t>21.42857142857143</t>
+  </si>
+  <si>
     <t>14:15:08.014</t>
   </si>
   <si>
     <t>14:41:36.785</t>
   </si>
   <si>
+    <t>88.23529411764706</t>
+  </si>
+  <si>
+    <t>11.764705882352942</t>
+  </si>
+  <si>
     <t>14:22:08.352</t>
   </si>
   <si>
     <t>14:45:59.368</t>
   </si>
   <si>
+    <t>84.61538461538461</t>
+  </si>
+  <si>
+    <t>15.384615384615387</t>
+  </si>
+  <si>
     <t>14:13:54.844</t>
   </si>
   <si>
     <t>14:29:18.332</t>
   </si>
   <si>
+    <t>84.21052631578948</t>
+  </si>
+  <si>
+    <t>15.78947368421052</t>
+  </si>
+  <si>
     <t>14:19:57.019</t>
   </si>
   <si>
     <t>14:33:28.259</t>
   </si>
   <si>
+    <t>88.88888888888889</t>
+  </si>
+  <si>
+    <t>11.111111111111114</t>
+  </si>
+  <si>
     <t>14:15:31.568</t>
   </si>
   <si>
     <t>14:40:03.212</t>
   </si>
   <si>
+    <t>95.0</t>
+  </si>
+  <si>
+    <t>5.0</t>
+  </si>
+  <si>
     <t>15:03:20.042</t>
   </si>
   <si>
     <t>15:20:07.463</t>
   </si>
   <si>
+    <t>0 planificado</t>
+  </si>
+  <si>
     <t>15:29:42.390</t>
   </si>
   <si>
     <t>15:55:50.529</t>
   </si>
   <si>
+    <t>62.5</t>
+  </si>
+  <si>
+    <t>37.5</t>
+  </si>
+  <si>
     <t>15:00:03.742</t>
   </si>
   <si>
     <t>15:36:46.952</t>
   </si>
   <si>
+    <t>95.23809523809524</t>
+  </si>
+  <si>
+    <t>4.761904761904759</t>
+  </si>
+  <si>
     <t>14:23:03.711</t>
   </si>
   <si>
     <t>14:47:23.112</t>
   </si>
   <si>
+    <t>92.85714285714286</t>
+  </si>
+  <si>
+    <t>7.142857142857139</t>
+  </si>
+  <si>
     <t>14:14:43.812</t>
   </si>
   <si>
     <t>14:44:49.452</t>
   </si>
   <si>
+    <t>93.75</t>
+  </si>
+  <si>
+    <t>6.25</t>
+  </si>
+  <si>
     <t>14:41:30.786</t>
   </si>
   <si>
     <t>14:55:21.747</t>
   </si>
   <si>
+    <t>76.47058823529412</t>
+  </si>
+  <si>
+    <t>23.529411764705884</t>
+  </si>
+  <si>
     <t>14:56:41.369</t>
   </si>
   <si>
     <t>15:12:14.966</t>
   </si>
   <si>
+    <t>86.66666666666667</t>
+  </si>
+  <si>
+    <t>13.333333333333329</t>
+  </si>
+  <si>
     <t>15:06:50.654</t>
   </si>
   <si>
     <t>15:43:52.114</t>
   </si>
   <si>
+    <t>83.33333333333333</t>
+  </si>
+  <si>
+    <t>16.66666666666667</t>
+  </si>
+  <si>
     <t>14:22:36.656</t>
   </si>
   <si>
     <t>14:50:51.188</t>
   </si>
   <si>
+    <t>81.25</t>
+  </si>
+  <si>
+    <t>18.75</t>
+  </si>
+  <si>
     <t>14:14:22.689</t>
   </si>
   <si>
     <t>14:32:03.553</t>
   </si>
   <si>
+    <t>92.5925925925926</t>
+  </si>
+  <si>
+    <t>7.407407407407405</t>
+  </si>
+  <si>
     <t>15:03:08.992</t>
   </si>
   <si>
@@ -206,24 +305,48 @@
     <t>15:51:25.871</t>
   </si>
   <si>
+    <t>90.3225806451613</t>
+  </si>
+  <si>
+    <t>9.677419354838705</t>
+  </si>
+  <si>
     <t>15:05:45.125</t>
   </si>
   <si>
     <t>15:51:06.619</t>
   </si>
   <si>
+    <t>90.9090909090909</t>
+  </si>
+  <si>
+    <t>9.090909090909093</t>
+  </si>
+  <si>
     <t>15:16:10.839</t>
   </si>
   <si>
     <t>15:43:29.980</t>
   </si>
   <si>
+    <t>94.73684210526316</t>
+  </si>
+  <si>
+    <t>5.263157894736835</t>
+  </si>
+  <si>
     <t>14:59:31.380</t>
   </si>
   <si>
     <t>15:53:03.221</t>
   </si>
   <si>
+    <t>88.63636363636364</t>
+  </si>
+  <si>
+    <t>11.36363636363636</t>
+  </si>
+  <si>
     <t>14:22:05.337</t>
   </si>
   <si>
@@ -236,12 +359,21 @@
     <t>15:29:19.230</t>
   </si>
   <si>
+    <t>50.0</t>
+  </si>
+  <si>
     <t>15:01:24.561</t>
   </si>
   <si>
     <t>15:51:01.360</t>
   </si>
   <si>
+    <t>76.74418604651163</t>
+  </si>
+  <si>
+    <t>23.25581395348837</t>
+  </si>
+  <si>
     <t>14:56:23.695</t>
   </si>
   <si>
@@ -254,24 +386,48 @@
     <t>15:42:14.394</t>
   </si>
   <si>
+    <t>87.5</t>
+  </si>
+  <si>
+    <t>12.5</t>
+  </si>
+  <si>
     <t>14:57:14.599</t>
   </si>
   <si>
     <t>15:25:56.336</t>
   </si>
   <si>
+    <t>100.0</t>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
     <t>14:58:10.940</t>
   </si>
   <si>
     <t>15:40:59.178</t>
   </si>
   <si>
+    <t>75.0</t>
+  </si>
+  <si>
+    <t>25.0</t>
+  </si>
+  <si>
     <t>15:04:46.232</t>
   </si>
   <si>
     <t>15:20:10.657</t>
   </si>
   <si>
+    <t>60.0</t>
+  </si>
+  <si>
+    <t>40.0</t>
+  </si>
+  <si>
     <t>15:07:30.038</t>
   </si>
   <si>
@@ -290,36 +446,72 @@
     <t>15:29:11.613</t>
   </si>
   <si>
+    <t>78.94736842105263</t>
+  </si>
+  <si>
+    <t>21.05263157894737</t>
+  </si>
+  <si>
     <t>15:01:05.153</t>
   </si>
   <si>
     <t>15:42:28.525</t>
   </si>
   <si>
+    <t>76.78571428571429</t>
+  </si>
+  <si>
+    <t>23.214285714285708</t>
+  </si>
+  <si>
     <t>14:41:32.880</t>
   </si>
   <si>
     <t>15:11:40.452</t>
   </si>
   <si>
+    <t>92.3076923076923</t>
+  </si>
+  <si>
+    <t>7.692307692307693</t>
+  </si>
+  <si>
     <t>14:59:05.674</t>
   </si>
   <si>
     <t>15:53:16.524</t>
   </si>
   <si>
+    <t>83.78378378378379</t>
+  </si>
+  <si>
+    <t>16.21621621621621</t>
+  </si>
+  <si>
     <t>14:21:40.891</t>
   </si>
   <si>
     <t>14:53:52.881</t>
   </si>
   <si>
+    <t>90.2439024390244</t>
+  </si>
+  <si>
+    <t>9.756097560975604</t>
+  </si>
+  <si>
     <t>14:13:26.720</t>
   </si>
   <si>
     <t>14:26:27.789</t>
   </si>
   <si>
+    <t>90.47619047619048</t>
+  </si>
+  <si>
+    <t>9.523809523809518</t>
+  </si>
+  <si>
     <t>16:03:16.527</t>
   </si>
   <si>
@@ -344,18 +536,36 @@
     <t>16:44:13.973</t>
   </si>
   <si>
+    <t>83.87096774193549</t>
+  </si>
+  <si>
+    <t>16.129032258064512</t>
+  </si>
+  <si>
     <t>15:55:15.139</t>
   </si>
   <si>
     <t>16:28:02.631</t>
   </si>
   <si>
+    <t>80.76923076923077</t>
+  </si>
+  <si>
+    <t>19.230769230769226</t>
+  </si>
+  <si>
     <t>15:54:22.013</t>
   </si>
   <si>
     <t>16:20:28.972</t>
   </si>
   <si>
+    <t>96.42857142857143</t>
+  </si>
+  <si>
+    <t>3.5714285714285694</t>
+  </si>
+  <si>
     <t>15:03:42.632</t>
   </si>
   <si>
@@ -374,6 +584,12 @@
     <t>17:06:26.439</t>
   </si>
   <si>
+    <t>80.95238095238095</t>
+  </si>
+  <si>
+    <t>19.04761904761905</t>
+  </si>
+  <si>
     <t>15:04:10.151</t>
   </si>
   <si>
@@ -392,6 +608,12 @@
     <t>15:48:01.202</t>
   </si>
   <si>
+    <t>78.78787878787878</t>
+  </si>
+  <si>
+    <t>21.212121212121218</t>
+  </si>
+  <si>
     <t>15:41:43.127</t>
   </si>
   <si>
@@ -404,12 +626,24 @@
     <t>15:22:04.958</t>
   </si>
   <si>
+    <t>57.142857142857146</t>
+  </si>
+  <si>
+    <t>42.857142857142854</t>
+  </si>
+  <si>
     <t>14:53:45.380</t>
   </si>
   <si>
     <t>15:43:28.720</t>
   </si>
   <si>
+    <t>90.0</t>
+  </si>
+  <si>
+    <t>10.0</t>
+  </si>
+  <si>
     <t>15:22:11.114</t>
   </si>
   <si>
@@ -434,12 +668,24 @@
     <t>17:01:27.938</t>
   </si>
   <si>
+    <t>94.11764705882354</t>
+  </si>
+  <si>
+    <t>5.882352941176464</t>
+  </si>
+  <si>
     <t>14:14:16.150</t>
   </si>
   <si>
     <t>15:22:37.565</t>
   </si>
   <si>
+    <t>83.60655737704919</t>
+  </si>
+  <si>
+    <t>16.393442622950815</t>
+  </si>
+  <si>
     <t>16:50:34.650</t>
   </si>
   <si>
@@ -452,12 +698,24 @@
     <t>14:45:28.411</t>
   </si>
   <si>
+    <t>91.66666666666667</t>
+  </si>
+  <si>
+    <t>8.333333333333329</t>
+  </si>
+  <si>
     <t>14:14:40.795</t>
   </si>
   <si>
     <t>14:32:00.853</t>
   </si>
   <si>
+    <t>90.625</t>
+  </si>
+  <si>
+    <t>9.375</t>
+  </si>
+  <si>
     <t>14:21:08.325</t>
   </si>
   <si>
@@ -470,12 +728,24 @@
     <t>15:20:21.395</t>
   </si>
   <si>
+    <t>89.28571428571429</t>
+  </si>
+  <si>
+    <t>10.714285714285708</t>
+  </si>
+  <si>
     <t>14:20:39.906</t>
   </si>
   <si>
     <t>15:41:36.914</t>
   </si>
   <si>
+    <t>56.25</t>
+  </si>
+  <si>
+    <t>43.75</t>
+  </si>
+  <si>
     <t>15:41:05.914</t>
   </si>
   <si>
@@ -500,12 +770,24 @@
     <t>15:18:33.196</t>
   </si>
   <si>
+    <t>96.29629629629629</t>
+  </si>
+  <si>
+    <t>3.7037037037037095</t>
+  </si>
+  <si>
     <t>15:04:56.808</t>
   </si>
   <si>
     <t>15:20:16.102</t>
   </si>
   <si>
+    <t>66.66666666666667</t>
+  </si>
+  <si>
+    <t>33.33333333333333</t>
+  </si>
+  <si>
     <t>14:45:53.780</t>
   </si>
   <si>
@@ -518,6 +800,12 @@
     <t>14:42:45.564</t>
   </si>
   <si>
+    <t>75.86206896551724</t>
+  </si>
+  <si>
+    <t>24.13793103448276</t>
+  </si>
+  <si>
     <t>14:21:37.576</t>
   </si>
   <si>
@@ -530,22 +818,46 @@
     <t>14:59:25.079</t>
   </si>
   <si>
+    <t>71.42857142857143</t>
+  </si>
+  <si>
+    <t>28.57142857142857</t>
+  </si>
+  <si>
     <t>14:13:42.166</t>
   </si>
   <si>
     <t>14:58:20.061</t>
   </si>
   <si>
+    <t>76.0</t>
+  </si>
+  <si>
+    <t>24.0</t>
+  </si>
+  <si>
     <t>15:19:07.753</t>
   </si>
   <si>
     <t>15:53:54.322</t>
   </si>
   <si>
+    <t>91.30434782608695</t>
+  </si>
+  <si>
+    <t>8.695652173913047</t>
+  </si>
+  <si>
     <t>16:01:37.196</t>
   </si>
   <si>
     <t>16:30:37.739</t>
+  </si>
+  <si>
+    <t>77.14285714285714</t>
+  </si>
+  <si>
+    <t>22.85714285714286</t>
   </si>
 </sst>
 </file>
@@ -665,30 +977,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{50A6CEB6-4828-4F49-9E76-DF7D506E60E9}" name="Tabla1" displayName="Tabla1" ref="A1:U76" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
-  <autoFilter ref="A1:U76" xr:uid="{50A6CEB6-4828-4F49-9E76-DF7D506E60E9}"/>
-  <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{6B4E22F2-2C14-45D0-920F-1717587B9237}" name="ID"/>
-    <tableColumn id="2" xr3:uid="{1E74DAF0-E0A7-4201-AEE6-2B1E556A4E4B}" name="Sesion"/>
-    <tableColumn id="3" xr3:uid="{8289B253-A5F2-4859-8E97-33C05307F919}" name="Num niveles"/>
-    <tableColumn id="4" xr3:uid="{910D759D-83C5-43D2-A5DC-DFD9371C0E28}" name="Num intentos"/>
-    <tableColumn id="5" xr3:uid="{62A5897B-EB67-427B-9C4F-AD4198969D00}" name="Completados"/>
-    <tableColumn id="6" xr3:uid="{19811FD8-36A0-4222-B3C5-B02B4EF64EAC}" name="Tiempo inicio"/>
-    <tableColumn id="7" xr3:uid="{DD9A5031-3EE2-47C4-BDCC-FAC4FF3901EB}" name="Tiempo final"/>
-    <tableColumn id="8" xr3:uid="{93751A20-8C0A-4EA5-B8A6-DA6B420FED58}" name="Tiempo duracion"/>
-    <tableColumn id="9" xr3:uid="{763F056A-07F5-4F9F-ACB0-FF6B08A43C14}" name="Pasos planificados"/>
-    <tableColumn id="10" xr3:uid="{61CFBBE7-B662-4238-93B7-278575A3217A}" name="Pasos ejecutados"/>
-    <tableColumn id="11" xr3:uid="{143CA440-15D4-4AD6-81F7-A785F9858561}" name="Errores ejecucion"/>
-    <tableColumn id="12" xr3:uid="{165F9EE3-E121-4453-ACEA-445902806BCD}" name="Num dormir planificado"/>
-    <tableColumn id="13" xr3:uid="{F8509A7F-9D55-4550-9D5C-3CED432058AB}" name="Correctos dormir"/>
-    <tableColumn id="14" xr3:uid="{BA1506CD-6815-4E63-8935-9F9D3C9DE0A0}" name="Errores dormir"/>
-    <tableColumn id="15" xr3:uid="{B06C4104-582A-4708-8C76-52BA3A2043FD}" name="Num ubicacion planificado"/>
-    <tableColumn id="16" xr3:uid="{3650B486-B227-4200-AC2A-7D435DED2464}" name="Correctos ubicacion"/>
-    <tableColumn id="17" xr3:uid="{0DB4E5B6-C149-41B6-8F95-A8CD8B2FDC92}" name="Errores ubicacion"/>
-    <tableColumn id="18" xr3:uid="{231C5930-9BDE-41CE-94A6-7939CB5CB8D0}" name="Paradas posibles"/>
-    <tableColumn id="19" xr3:uid="{DB28CEAA-6E16-48AB-89E6-E31999C62676}" name="Paradas realizadas"/>
-    <tableColumn id="20" xr3:uid="{BD09F00A-31DA-45A6-89A0-7023FD012282}" name="Errores parada por tiempo excedido"/>
-    <tableColumn id="21" xr3:uid="{7E4DD15D-11D9-4755-A89F-A0F9EB1B9AE3}" name="Num errores por tiempo excedido"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A4099921-2F47-4780-A08B-0D05EB9D2D81}" name="Tabla1" displayName="Tabla1" ref="A1:W76" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
+  <autoFilter ref="A1:W76" xr:uid="{A4099921-2F47-4780-A08B-0D05EB9D2D81}"/>
+  <tableColumns count="23">
+    <tableColumn id="1" xr3:uid="{6576FD01-423D-418E-91CA-C5B75C6BBE93}" name="ID"/>
+    <tableColumn id="2" xr3:uid="{28C1E850-1B71-4C47-A505-55FDB8ABB9EC}" name="Sesion"/>
+    <tableColumn id="3" xr3:uid="{7475987C-2DFB-4F3F-AE38-0632A8F5F61E}" name="Num niveles"/>
+    <tableColumn id="4" xr3:uid="{6A777A5E-6F56-43DB-9D89-7DD432852EF6}" name="Num intentos"/>
+    <tableColumn id="5" xr3:uid="{DC0AAE82-027A-46D0-A78A-AF267F8831D5}" name="Completados"/>
+    <tableColumn id="6" xr3:uid="{799C8FCD-BCD9-4115-AC14-686F3AAC9AD3}" name="Tiempo inicio"/>
+    <tableColumn id="7" xr3:uid="{DA142E27-FA10-41D4-827D-354225216331}" name="Tiempo final"/>
+    <tableColumn id="8" xr3:uid="{81151D87-607B-4BB6-B513-721BE055C595}" name="Tiempo duracion"/>
+    <tableColumn id="9" xr3:uid="{4AD555CC-E537-4AAC-9138-3EE17EE4C5EB}" name="Pasos planificados"/>
+    <tableColumn id="10" xr3:uid="{2969C28B-5436-4AFD-94F3-BA22A02A0107}" name="Pasos ejecutados"/>
+    <tableColumn id="11" xr3:uid="{28D961FD-A200-4AC7-993D-FD0C715C540B}" name="Errores ejecucion"/>
+    <tableColumn id="12" xr3:uid="{66A9D3CF-D9CB-4490-9499-147DA52BBE25}" name="Num dormir planificado"/>
+    <tableColumn id="13" xr3:uid="{5B3E66C8-4EC5-40A1-A6C8-3BEA0E54ECCE}" name="Correctos dormir"/>
+    <tableColumn id="14" xr3:uid="{EE608BA7-D83D-4062-ABE1-B6BB6F5D2B79}" name="Errores dormir"/>
+    <tableColumn id="15" xr3:uid="{E8A88115-6D06-4157-A411-695F3E2C829C}" name="Num ubicacion planificado"/>
+    <tableColumn id="16" xr3:uid="{7772CEA8-5659-4CAE-B071-6E70CC791C25}" name="Correctos ubicacion"/>
+    <tableColumn id="17" xr3:uid="{AA1D357A-1E0C-4943-BACF-C4035EA7E922}" name="Errores ubicacion"/>
+    <tableColumn id="18" xr3:uid="{64690D29-9288-4C92-92B0-D1A869F516BB}" name="Paradas posibles"/>
+    <tableColumn id="19" xr3:uid="{A0834F24-6F65-44E3-8BF1-C307014C19F3}" name="Paradas realizadas"/>
+    <tableColumn id="20" xr3:uid="{523CDB9E-E37A-4168-ADE6-9F32A8FC7EE7}" name="Errores parada por tiempo excedido"/>
+    <tableColumn id="21" xr3:uid="{E7DE7E80-7773-4015-B8AE-EB0425FFD465}" name="Num errores por tiempo excedido"/>
+    <tableColumn id="22" xr3:uid="{EBFC6435-729C-426A-B312-CD78C3FE3651}" name="% Aciertos"/>
+    <tableColumn id="23" xr3:uid="{E667AA5D-8CBA-443E-845B-C36AC954AE19}" name="% Mal"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -979,7 +1293,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U76"/>
+  <dimension ref="A1:W76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="13.21875" customWidth="1"/>
@@ -1000,9 +1314,10 @@
     <col min="19" max="19" width="18.21875" customWidth="1"/>
     <col min="20" max="20" width="32.88671875" customWidth="1"/>
     <col min="21" max="21" width="31.109375" customWidth="1"/>
+    <col min="22" max="23" width="18.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1066,8 +1381,14 @@
       <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>10</v>
       </c>
@@ -1084,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H2">
         <v>1001.4829999999999</v>
@@ -1131,8 +1452,14 @@
       <c r="U2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>10</v>
       </c>
@@ -1149,10 +1476,10 @@
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H3">
         <v>1588.771</v>
@@ -1196,8 +1523,14 @@
       <c r="U3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V3" t="s">
+        <v>29</v>
+      </c>
+      <c r="W3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>11</v>
       </c>
@@ -1214,10 +1547,10 @@
         <v>4</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H4">
         <v>1431.0160000000001</v>
@@ -1261,8 +1594,14 @@
       <c r="U4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V4" t="s">
+        <v>33</v>
+      </c>
+      <c r="W4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>11</v>
       </c>
@@ -1279,10 +1618,10 @@
         <v>3</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="H5">
         <v>923.48800000000006</v>
@@ -1326,8 +1665,14 @@
       <c r="U5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V5" t="s">
+        <v>37</v>
+      </c>
+      <c r="W5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>13</v>
       </c>
@@ -1344,10 +1689,10 @@
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H6">
         <v>811.24</v>
@@ -1391,8 +1736,14 @@
       <c r="U6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V6" t="s">
+        <v>41</v>
+      </c>
+      <c r="W6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>13</v>
       </c>
@@ -1409,10 +1760,10 @@
         <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="G7" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="H7">
         <v>1471.644</v>
@@ -1456,8 +1807,14 @@
       <c r="U7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V7" t="s">
+        <v>45</v>
+      </c>
+      <c r="W7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>15</v>
       </c>
@@ -1474,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="G8" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="H8">
         <v>1007.421</v>
@@ -1521,8 +1878,14 @@
       <c r="U8">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V8" t="s">
+        <v>49</v>
+      </c>
+      <c r="W8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>16</v>
       </c>
@@ -1539,10 +1902,10 @@
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="G9" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="H9">
         <v>1568.1389999999999</v>
@@ -1586,8 +1949,14 @@
       <c r="U9">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V9" t="s">
+        <v>52</v>
+      </c>
+      <c r="W9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>16</v>
       </c>
@@ -1604,10 +1973,10 @@
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="G10" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="H10">
         <v>2203.21</v>
@@ -1651,8 +2020,14 @@
       <c r="U10">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V10" t="s">
+        <v>56</v>
+      </c>
+      <c r="W10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>17</v>
       </c>
@@ -1669,10 +2044,10 @@
         <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="G11" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="H11">
         <v>1459.4010000000001</v>
@@ -1716,8 +2091,14 @@
       <c r="U11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V11" t="s">
+        <v>60</v>
+      </c>
+      <c r="W11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>17</v>
       </c>
@@ -1734,10 +2115,10 @@
         <v>0</v>
       </c>
       <c r="F12" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="G12" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="H12">
         <v>1805.64</v>
@@ -1781,8 +2162,14 @@
       <c r="U12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V12" t="s">
+        <v>64</v>
+      </c>
+      <c r="W12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>18</v>
       </c>
@@ -1799,10 +2186,10 @@
         <v>0</v>
       </c>
       <c r="F13" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="G13" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="H13">
         <v>830.96100000000001</v>
@@ -1846,8 +2233,14 @@
       <c r="U13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V13" t="s">
+        <v>68</v>
+      </c>
+      <c r="W13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>18</v>
       </c>
@@ -1864,10 +2257,10 @@
         <v>3</v>
       </c>
       <c r="F14" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="G14" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="H14">
         <v>933.59699999999998</v>
@@ -1911,8 +2304,14 @@
       <c r="U14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V14" t="s">
+        <v>72</v>
+      </c>
+      <c r="W14" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>18</v>
       </c>
@@ -1929,10 +2328,10 @@
         <v>3</v>
       </c>
       <c r="F15" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="G15" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="H15">
         <v>2221.46</v>
@@ -1976,8 +2375,14 @@
       <c r="U15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V15" t="s">
+        <v>76</v>
+      </c>
+      <c r="W15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>19</v>
       </c>
@@ -1994,10 +2399,10 @@
         <v>4</v>
       </c>
       <c r="F16" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="G16" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="H16">
         <v>1694.5319999999999</v>
@@ -2041,8 +2446,14 @@
       <c r="U16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V16" t="s">
+        <v>80</v>
+      </c>
+      <c r="W16" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>19</v>
       </c>
@@ -2059,10 +2470,10 @@
         <v>4</v>
       </c>
       <c r="F17" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="G17" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="H17">
         <v>1060.864</v>
@@ -2106,8 +2517,14 @@
       <c r="U17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V17" t="s">
+        <v>84</v>
+      </c>
+      <c r="W17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1</v>
       </c>
@@ -2124,10 +2541,10 @@
         <v>0</v>
       </c>
       <c r="F18" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="G18" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="H18">
         <v>430.90499999999997</v>
@@ -2171,8 +2588,14 @@
       <c r="U18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V18" t="s">
+        <v>49</v>
+      </c>
+      <c r="W18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>21</v>
       </c>
@@ -2189,10 +2612,10 @@
         <v>0</v>
       </c>
       <c r="F19" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="G19" t="s">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="H19">
         <v>1570.5830000000001</v>
@@ -2236,8 +2659,14 @@
       <c r="U19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V19" t="s">
+        <v>90</v>
+      </c>
+      <c r="W19" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>21</v>
       </c>
@@ -2254,10 +2683,10 @@
         <v>4</v>
       </c>
       <c r="F20" t="s">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="G20" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="H20">
         <v>2721.4940000000001</v>
@@ -2301,8 +2730,14 @@
       <c r="U20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V20" t="s">
+        <v>94</v>
+      </c>
+      <c r="W20" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>22</v>
       </c>
@@ -2319,10 +2754,10 @@
         <v>2</v>
       </c>
       <c r="F21" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="G21" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="H21">
         <v>1639.1410000000001</v>
@@ -2366,8 +2801,14 @@
       <c r="U21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V21" t="s">
+        <v>98</v>
+      </c>
+      <c r="W21" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>22</v>
       </c>
@@ -2384,10 +2825,10 @@
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="G22" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="H22">
         <v>3211.8409999999999</v>
@@ -2431,8 +2872,14 @@
       <c r="U22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V22" t="s">
+        <v>102</v>
+      </c>
+      <c r="W22" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>23</v>
       </c>
@@ -2449,10 +2896,10 @@
         <v>0</v>
       </c>
       <c r="F23" t="s">
-        <v>63</v>
+        <v>104</v>
       </c>
       <c r="G23" t="s">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="H23">
         <v>1882.586</v>
@@ -2496,8 +2943,14 @@
       <c r="U23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V23" t="s">
+        <v>25</v>
+      </c>
+      <c r="W23" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>24</v>
       </c>
@@ -2514,10 +2967,10 @@
         <v>0</v>
       </c>
       <c r="F24" t="s">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="G24" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="H24">
         <v>1136.1980000000001</v>
@@ -2561,8 +3014,14 @@
       <c r="U24">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V24" t="s">
+        <v>108</v>
+      </c>
+      <c r="W24" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2579,10 +3038,10 @@
         <v>2</v>
       </c>
       <c r="F25" t="s">
-        <v>67</v>
+        <v>109</v>
       </c>
       <c r="G25" t="s">
-        <v>68</v>
+        <v>110</v>
       </c>
       <c r="H25">
         <v>2976.799</v>
@@ -2626,8 +3085,14 @@
       <c r="U25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V25" t="s">
+        <v>111</v>
+      </c>
+      <c r="W25" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2644,10 +3109,10 @@
         <v>0</v>
       </c>
       <c r="F26" t="s">
-        <v>69</v>
+        <v>113</v>
       </c>
       <c r="G26" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="H26">
         <v>1595.1990000000001</v>
@@ -2691,8 +3156,14 @@
       <c r="U26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V26" t="s">
+        <v>45</v>
+      </c>
+      <c r="W26" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>25</v>
       </c>
@@ -2709,10 +3180,10 @@
         <v>0</v>
       </c>
       <c r="F27" t="s">
-        <v>71</v>
+        <v>115</v>
       </c>
       <c r="G27" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="H27">
         <v>2688.6970000000001</v>
@@ -2756,8 +3227,14 @@
       <c r="U27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V27" t="s">
+        <v>117</v>
+      </c>
+      <c r="W27" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26</v>
       </c>
@@ -2774,10 +3251,10 @@
         <v>0</v>
       </c>
       <c r="F28" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="G28" t="s">
-        <v>74</v>
+        <v>120</v>
       </c>
       <c r="H28">
         <v>1721.7370000000001</v>
@@ -2821,8 +3298,14 @@
       <c r="U28">
         <v>2</v>
       </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V28" t="s">
+        <v>121</v>
+      </c>
+      <c r="W28" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26</v>
       </c>
@@ -2839,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>75</v>
+        <v>123</v>
       </c>
       <c r="G29" t="s">
-        <v>76</v>
+        <v>124</v>
       </c>
       <c r="H29">
         <v>2568.2379999999998</v>
@@ -2886,8 +3369,14 @@
       <c r="U29">
         <v>2</v>
       </c>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V29" t="s">
+        <v>125</v>
+      </c>
+      <c r="W29" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>27</v>
       </c>
@@ -2904,10 +3393,10 @@
         <v>0</v>
       </c>
       <c r="F30" t="s">
-        <v>77</v>
+        <v>127</v>
       </c>
       <c r="G30" t="s">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="H30">
         <v>924.42499999999995</v>
@@ -2951,8 +3440,14 @@
       <c r="U30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V30" t="s">
+        <v>129</v>
+      </c>
+      <c r="W30" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>27</v>
       </c>
@@ -2969,10 +3464,10 @@
         <v>0</v>
       </c>
       <c r="F31" t="s">
-        <v>79</v>
+        <v>131</v>
       </c>
       <c r="G31" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="H31">
         <v>2739.4659999999999</v>
@@ -3016,8 +3511,14 @@
       <c r="U31">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V31" t="s">
+        <v>125</v>
+      </c>
+      <c r="W31" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>2</v>
       </c>
@@ -3034,10 +3535,10 @@
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="G32" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="H32">
         <v>2110.4520000000002</v>
@@ -3081,8 +3582,14 @@
       <c r="U32">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V32" t="s">
+        <v>117</v>
+      </c>
+      <c r="W32" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>30</v>
       </c>
@@ -3099,10 +3606,10 @@
         <v>3</v>
       </c>
       <c r="F33" t="s">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="G33" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="H33">
         <v>1783.269</v>
@@ -3146,8 +3653,14 @@
       <c r="U33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V33" t="s">
+        <v>137</v>
+      </c>
+      <c r="W33" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>30</v>
       </c>
@@ -3164,10 +3677,10 @@
         <v>4</v>
       </c>
       <c r="F34" t="s">
-        <v>85</v>
+        <v>139</v>
       </c>
       <c r="G34" t="s">
-        <v>86</v>
+        <v>140</v>
       </c>
       <c r="H34">
         <v>2483.3719999999998</v>
@@ -3211,8 +3724,14 @@
       <c r="U34">
         <v>2</v>
       </c>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V34" t="s">
+        <v>141</v>
+      </c>
+      <c r="W34" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>31</v>
       </c>
@@ -3229,10 +3748,10 @@
         <v>0</v>
       </c>
       <c r="F35" t="s">
-        <v>87</v>
+        <v>143</v>
       </c>
       <c r="G35" t="s">
-        <v>88</v>
+        <v>144</v>
       </c>
       <c r="H35">
         <v>1807.5719999999999</v>
@@ -3276,8 +3795,14 @@
       <c r="U35">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V35" t="s">
+        <v>145</v>
+      </c>
+      <c r="W35" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>31</v>
       </c>
@@ -3294,10 +3819,10 @@
         <v>0</v>
       </c>
       <c r="F36" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="G36" t="s">
-        <v>90</v>
+        <v>148</v>
       </c>
       <c r="H36">
         <v>3250.85</v>
@@ -3341,8 +3866,14 @@
       <c r="U36">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V36" t="s">
+        <v>149</v>
+      </c>
+      <c r="W36" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>32</v>
       </c>
@@ -3359,10 +3890,10 @@
         <v>2</v>
       </c>
       <c r="F37" t="s">
-        <v>91</v>
+        <v>151</v>
       </c>
       <c r="G37" t="s">
-        <v>92</v>
+        <v>152</v>
       </c>
       <c r="H37">
         <v>1931.99</v>
@@ -3406,8 +3937,14 @@
       <c r="U37">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V37" t="s">
+        <v>153</v>
+      </c>
+      <c r="W37" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>32</v>
       </c>
@@ -3424,10 +3961,10 @@
         <v>3</v>
       </c>
       <c r="F38" t="s">
-        <v>93</v>
+        <v>155</v>
       </c>
       <c r="G38" t="s">
-        <v>94</v>
+        <v>156</v>
       </c>
       <c r="H38">
         <v>781.06899999999996</v>
@@ -3471,8 +4008,14 @@
       <c r="U38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V38" t="s">
+        <v>157</v>
+      </c>
+      <c r="W38" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>33</v>
       </c>
@@ -3489,10 +4032,10 @@
         <v>0</v>
       </c>
       <c r="F39" t="s">
-        <v>95</v>
+        <v>159</v>
       </c>
       <c r="G39" t="s">
-        <v>96</v>
+        <v>160</v>
       </c>
       <c r="H39">
         <v>1462.616</v>
@@ -3536,8 +4079,14 @@
       <c r="U39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V39" t="s">
+        <v>49</v>
+      </c>
+      <c r="W39" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>34</v>
       </c>
@@ -3554,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="F40" t="s">
-        <v>97</v>
+        <v>161</v>
       </c>
       <c r="G40" t="s">
-        <v>98</v>
+        <v>162</v>
       </c>
       <c r="H40">
         <v>1267.6220000000001</v>
@@ -3601,8 +4150,14 @@
       <c r="U40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V40" t="s">
+        <v>49</v>
+      </c>
+      <c r="W40" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>35</v>
       </c>
@@ -3619,10 +4174,10 @@
         <v>0</v>
       </c>
       <c r="F41" t="s">
-        <v>99</v>
+        <v>163</v>
       </c>
       <c r="G41" t="s">
-        <v>100</v>
+        <v>164</v>
       </c>
       <c r="H41">
         <v>1885.146</v>
@@ -3666,8 +4221,14 @@
       <c r="U41">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V41" t="s">
+        <v>49</v>
+      </c>
+      <c r="W41" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>35</v>
       </c>
@@ -3684,10 +4245,10 @@
         <v>0</v>
       </c>
       <c r="F42" t="s">
-        <v>101</v>
+        <v>165</v>
       </c>
       <c r="G42" t="s">
-        <v>102</v>
+        <v>166</v>
       </c>
       <c r="H42">
         <v>3121.1120000000001</v>
@@ -3731,8 +4292,14 @@
       <c r="U42">
         <v>2</v>
       </c>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V42" t="s">
+        <v>167</v>
+      </c>
+      <c r="W42" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>37</v>
       </c>
@@ -3749,10 +4316,10 @@
         <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>103</v>
+        <v>169</v>
       </c>
       <c r="G43" t="s">
-        <v>104</v>
+        <v>170</v>
       </c>
       <c r="H43">
         <v>1967.492</v>
@@ -3796,8 +4363,14 @@
       <c r="U43">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V43" t="s">
+        <v>171</v>
+      </c>
+      <c r="W43" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>37</v>
       </c>
@@ -3814,10 +4387,10 @@
         <v>1</v>
       </c>
       <c r="F44" t="s">
-        <v>105</v>
+        <v>173</v>
       </c>
       <c r="G44" t="s">
-        <v>106</v>
+        <v>174</v>
       </c>
       <c r="H44">
         <v>1566.9590000000001</v>
@@ -3861,8 +4434,14 @@
       <c r="U44">
         <v>2</v>
       </c>
-    </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V44" t="s">
+        <v>175</v>
+      </c>
+      <c r="W44" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>3</v>
       </c>
@@ -3879,10 +4458,10 @@
         <v>0</v>
       </c>
       <c r="F45" t="s">
-        <v>107</v>
+        <v>177</v>
       </c>
       <c r="G45" t="s">
-        <v>108</v>
+        <v>178</v>
       </c>
       <c r="H45">
         <v>7.0000000000000001E-3</v>
@@ -3926,8 +4505,14 @@
       <c r="U45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V45" t="s">
+        <v>49</v>
+      </c>
+      <c r="W45" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>3</v>
       </c>
@@ -3944,10 +4529,10 @@
         <v>0</v>
       </c>
       <c r="F46" t="s">
-        <v>109</v>
+        <v>179</v>
       </c>
       <c r="G46" t="s">
-        <v>110</v>
+        <v>180</v>
       </c>
       <c r="H46">
         <v>379.57600000000002</v>
@@ -3991,8 +4576,14 @@
       <c r="U46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V46" t="s">
+        <v>49</v>
+      </c>
+      <c r="W46" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>41</v>
       </c>
@@ -4009,10 +4600,10 @@
         <v>1</v>
       </c>
       <c r="F47" t="s">
-        <v>111</v>
+        <v>181</v>
       </c>
       <c r="G47" t="s">
-        <v>112</v>
+        <v>182</v>
       </c>
       <c r="H47">
         <v>1186.057</v>
@@ -4056,8 +4647,14 @@
       <c r="U47">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V47" t="s">
+        <v>183</v>
+      </c>
+      <c r="W47" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>42</v>
       </c>
@@ -4074,10 +4671,10 @@
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>113</v>
+        <v>185</v>
       </c>
       <c r="G48" t="s">
-        <v>114</v>
+        <v>186</v>
       </c>
       <c r="H48">
         <v>1128.722</v>
@@ -4121,8 +4718,14 @@
       <c r="U48">
         <v>2</v>
       </c>
-    </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V48" t="s">
+        <v>49</v>
+      </c>
+      <c r="W48" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>43</v>
       </c>
@@ -4139,10 +4742,10 @@
         <v>0</v>
       </c>
       <c r="F49" t="s">
-        <v>115</v>
+        <v>187</v>
       </c>
       <c r="G49" t="s">
-        <v>116</v>
+        <v>188</v>
       </c>
       <c r="H49">
         <v>1324.854</v>
@@ -4186,8 +4789,14 @@
       <c r="U49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V49" t="s">
+        <v>41</v>
+      </c>
+      <c r="W49" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>43</v>
       </c>
@@ -4204,10 +4813,10 @@
         <v>1</v>
       </c>
       <c r="F50" t="s">
-        <v>117</v>
+        <v>189</v>
       </c>
       <c r="G50" t="s">
-        <v>118</v>
+        <v>190</v>
       </c>
       <c r="H50">
         <v>1245.463</v>
@@ -4251,8 +4860,14 @@
       <c r="U50">
         <v>2</v>
       </c>
-    </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V50" t="s">
+        <v>191</v>
+      </c>
+      <c r="W50" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>44</v>
       </c>
@@ -4269,10 +4884,10 @@
         <v>0</v>
       </c>
       <c r="F51" t="s">
-        <v>119</v>
+        <v>193</v>
       </c>
       <c r="G51" t="s">
-        <v>120</v>
+        <v>194</v>
       </c>
       <c r="H51">
         <v>744.75</v>
@@ -4316,8 +4931,14 @@
       <c r="U51">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V51" t="s">
+        <v>49</v>
+      </c>
+      <c r="W51" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>45</v>
       </c>
@@ -4334,10 +4955,10 @@
         <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>121</v>
+        <v>195</v>
       </c>
       <c r="G52" t="s">
-        <v>122</v>
+        <v>196</v>
       </c>
       <c r="H52">
         <v>1124.6210000000001</v>
@@ -4381,8 +5002,14 @@
       <c r="U52">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V52" t="s">
+        <v>197</v>
+      </c>
+      <c r="W52" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>45</v>
       </c>
@@ -4399,10 +5026,10 @@
         <v>3</v>
       </c>
       <c r="F53" t="s">
-        <v>123</v>
+        <v>199</v>
       </c>
       <c r="G53" t="s">
-        <v>124</v>
+        <v>200</v>
       </c>
       <c r="H53">
         <v>2983.34</v>
@@ -4446,8 +5073,14 @@
       <c r="U53">
         <v>6</v>
       </c>
-    </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V53" t="s">
+        <v>201</v>
+      </c>
+      <c r="W53" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>46</v>
       </c>
@@ -4464,10 +5097,10 @@
         <v>0</v>
       </c>
       <c r="F54" t="s">
-        <v>125</v>
+        <v>203</v>
       </c>
       <c r="G54" t="s">
-        <v>126</v>
+        <v>204</v>
       </c>
       <c r="H54">
         <v>791.346</v>
@@ -4511,8 +5144,14 @@
       <c r="U54">
         <v>2</v>
       </c>
-    </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V54" t="s">
+        <v>125</v>
+      </c>
+      <c r="W54" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>47</v>
       </c>
@@ -4529,10 +5168,10 @@
         <v>0</v>
       </c>
       <c r="F55" t="s">
-        <v>127</v>
+        <v>205</v>
       </c>
       <c r="G55" t="s">
-        <v>128</v>
+        <v>206</v>
       </c>
       <c r="H55">
         <v>302.63299999999998</v>
@@ -4576,8 +5215,14 @@
       <c r="U55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V55" t="s">
+        <v>121</v>
+      </c>
+      <c r="W55" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>47</v>
       </c>
@@ -4594,10 +5239,10 @@
         <v>1</v>
       </c>
       <c r="F56" t="s">
-        <v>129</v>
+        <v>207</v>
       </c>
       <c r="G56" t="s">
-        <v>130</v>
+        <v>208</v>
       </c>
       <c r="H56">
         <v>3785.3609999999999</v>
@@ -4641,8 +5286,14 @@
       <c r="U56">
         <v>7</v>
       </c>
-    </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V56" t="s">
+        <v>108</v>
+      </c>
+      <c r="W56" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>48</v>
       </c>
@@ -4659,10 +5310,10 @@
         <v>1</v>
       </c>
       <c r="F57" t="s">
-        <v>131</v>
+        <v>209</v>
       </c>
       <c r="G57" t="s">
-        <v>132</v>
+        <v>210</v>
       </c>
       <c r="H57">
         <v>2002.558</v>
@@ -4706,8 +5357,14 @@
       <c r="U57">
         <v>2</v>
       </c>
-    </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V57" t="s">
+        <v>211</v>
+      </c>
+      <c r="W57" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="58" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>4</v>
       </c>
@@ -4724,10 +5381,10 @@
         <v>1</v>
       </c>
       <c r="F58" t="s">
-        <v>133</v>
+        <v>213</v>
       </c>
       <c r="G58" t="s">
-        <v>134</v>
+        <v>214</v>
       </c>
       <c r="H58">
         <v>4101.415</v>
@@ -4771,8 +5428,14 @@
       <c r="U58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V58" t="s">
+        <v>215</v>
+      </c>
+      <c r="W58" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>50</v>
       </c>
@@ -4789,10 +5452,10 @@
         <v>1</v>
       </c>
       <c r="F59" t="s">
-        <v>135</v>
+        <v>217</v>
       </c>
       <c r="G59" t="s">
-        <v>136</v>
+        <v>218</v>
       </c>
       <c r="H59">
         <v>1904.759</v>
@@ -4836,8 +5499,14 @@
       <c r="U59">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V59" t="s">
+        <v>197</v>
+      </c>
+      <c r="W59" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>51</v>
       </c>
@@ -4854,10 +5523,10 @@
         <v>4</v>
       </c>
       <c r="F60" t="s">
-        <v>137</v>
+        <v>219</v>
       </c>
       <c r="G60" t="s">
-        <v>138</v>
+        <v>220</v>
       </c>
       <c r="H60">
         <v>1371.93</v>
@@ -4901,8 +5570,14 @@
       <c r="U60">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V60" t="s">
+        <v>221</v>
+      </c>
+      <c r="W60" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="61" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>51</v>
       </c>
@@ -4919,10 +5594,10 @@
         <v>3</v>
       </c>
       <c r="F61" t="s">
-        <v>139</v>
+        <v>223</v>
       </c>
       <c r="G61" t="s">
-        <v>140</v>
+        <v>224</v>
       </c>
       <c r="H61">
         <v>1040.058</v>
@@ -4966,8 +5641,14 @@
       <c r="U61">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V61" t="s">
+        <v>225</v>
+      </c>
+      <c r="W61" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>52</v>
       </c>
@@ -4984,10 +5665,10 @@
         <v>0</v>
       </c>
       <c r="F62" t="s">
-        <v>141</v>
+        <v>227</v>
       </c>
       <c r="G62" t="s">
-        <v>142</v>
+        <v>228</v>
       </c>
       <c r="H62">
         <v>1945.4490000000001</v>
@@ -5031,8 +5712,14 @@
       <c r="U62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V62" t="s">
+        <v>72</v>
+      </c>
+      <c r="W62" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="63" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>53</v>
       </c>
@@ -5049,10 +5736,10 @@
         <v>3</v>
       </c>
       <c r="F63" t="s">
-        <v>143</v>
+        <v>229</v>
       </c>
       <c r="G63" t="s">
-        <v>144</v>
+        <v>230</v>
       </c>
       <c r="H63">
         <v>2758.1469999999999</v>
@@ -5096,8 +5783,14 @@
       <c r="U63">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V63" t="s">
+        <v>231</v>
+      </c>
+      <c r="W63" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>5</v>
       </c>
@@ -5114,10 +5807,10 @@
         <v>0</v>
       </c>
       <c r="F64" t="s">
-        <v>145</v>
+        <v>233</v>
       </c>
       <c r="G64" t="s">
-        <v>146</v>
+        <v>234</v>
       </c>
       <c r="H64">
         <v>4857.0079999999998</v>
@@ -5161,8 +5854,14 @@
       <c r="U64">
         <v>3</v>
       </c>
-    </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V64" t="s">
+        <v>235</v>
+      </c>
+      <c r="W64" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>65</v>
       </c>
@@ -5179,10 +5878,10 @@
         <v>1</v>
       </c>
       <c r="F65" t="s">
-        <v>147</v>
+        <v>237</v>
       </c>
       <c r="G65" t="s">
-        <v>148</v>
+        <v>238</v>
       </c>
       <c r="H65">
         <v>136.624</v>
@@ -5226,8 +5925,14 @@
       <c r="U65">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V65" t="s">
+        <v>121</v>
+      </c>
+      <c r="W65" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>6</v>
       </c>
@@ -5244,10 +5949,10 @@
         <v>0</v>
       </c>
       <c r="F66" t="s">
-        <v>149</v>
+        <v>239</v>
       </c>
       <c r="G66" t="s">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="H66">
         <v>1212.942</v>
@@ -5291,8 +5996,14 @@
       <c r="U66">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V66" t="s">
+        <v>125</v>
+      </c>
+      <c r="W66" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="67" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>6</v>
       </c>
@@ -5309,10 +6020,10 @@
         <v>2</v>
       </c>
       <c r="F67" t="s">
-        <v>151</v>
+        <v>241</v>
       </c>
       <c r="G67" t="s">
-        <v>152</v>
+        <v>242</v>
       </c>
       <c r="H67">
         <v>585.04700000000003</v>
@@ -5356,8 +6067,14 @@
       <c r="U67">
         <v>1</v>
       </c>
-    </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V67" t="s">
+        <v>145</v>
+      </c>
+      <c r="W67" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>6</v>
       </c>
@@ -5374,10 +6091,10 @@
         <v>3</v>
       </c>
       <c r="F68" t="s">
-        <v>153</v>
+        <v>243</v>
       </c>
       <c r="G68" t="s">
-        <v>154</v>
+        <v>244</v>
       </c>
       <c r="H68">
         <v>1203.318</v>
@@ -5421,8 +6138,14 @@
       <c r="U68">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V68" t="s">
+        <v>245</v>
+      </c>
+      <c r="W68" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>7</v>
       </c>
@@ -5439,10 +6162,10 @@
         <v>0</v>
       </c>
       <c r="F69" t="s">
-        <v>155</v>
+        <v>247</v>
       </c>
       <c r="G69" t="s">
-        <v>156</v>
+        <v>248</v>
       </c>
       <c r="H69">
         <v>919.29399999999998</v>
@@ -5486,8 +6209,14 @@
       <c r="U69">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V69" t="s">
+        <v>249</v>
+      </c>
+      <c r="W69" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>7</v>
       </c>
@@ -5504,10 +6233,10 @@
         <v>0</v>
       </c>
       <c r="F70" t="s">
-        <v>157</v>
+        <v>251</v>
       </c>
       <c r="G70" t="s">
-        <v>158</v>
+        <v>252</v>
       </c>
       <c r="H70">
         <v>33.176000000000002</v>
@@ -5551,8 +6280,14 @@
       <c r="U70">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V70" t="s">
+        <v>49</v>
+      </c>
+      <c r="W70" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>7</v>
       </c>
@@ -5569,10 +6304,10 @@
         <v>0</v>
       </c>
       <c r="F71" t="s">
-        <v>159</v>
+        <v>253</v>
       </c>
       <c r="G71" t="s">
-        <v>160</v>
+        <v>254</v>
       </c>
       <c r="H71">
         <v>1650.8009999999999</v>
@@ -5616,8 +6351,14 @@
       <c r="U71">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V71" t="s">
+        <v>255</v>
+      </c>
+      <c r="W71" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>8</v>
       </c>
@@ -5634,10 +6375,10 @@
         <v>0</v>
       </c>
       <c r="F72" t="s">
-        <v>161</v>
+        <v>257</v>
       </c>
       <c r="G72" t="s">
-        <v>162</v>
+        <v>258</v>
       </c>
       <c r="H72">
         <v>979.68100000000004</v>
@@ -5681,8 +6422,14 @@
       <c r="U72">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V72" t="s">
+        <v>49</v>
+      </c>
+      <c r="W72" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="73" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>8</v>
       </c>
@@ -5699,10 +6446,10 @@
         <v>0</v>
       </c>
       <c r="F73" t="s">
-        <v>163</v>
+        <v>259</v>
       </c>
       <c r="G73" t="s">
-        <v>164</v>
+        <v>260</v>
       </c>
       <c r="H73">
         <v>1146.846</v>
@@ -5746,8 +6493,14 @@
       <c r="U73">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V73" t="s">
+        <v>261</v>
+      </c>
+      <c r="W73" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>8</v>
       </c>
@@ -5764,10 +6517,10 @@
         <v>0</v>
       </c>
       <c r="F74" t="s">
-        <v>165</v>
+        <v>263</v>
       </c>
       <c r="G74" t="s">
-        <v>166</v>
+        <v>264</v>
       </c>
       <c r="H74">
         <v>2677.895</v>
@@ -5811,8 +6564,14 @@
       <c r="U74">
         <v>2</v>
       </c>
-    </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V74" t="s">
+        <v>265</v>
+      </c>
+      <c r="W74" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>9</v>
       </c>
@@ -5829,10 +6588,10 @@
         <v>4</v>
       </c>
       <c r="F75" t="s">
-        <v>167</v>
+        <v>267</v>
       </c>
       <c r="G75" t="s">
-        <v>168</v>
+        <v>268</v>
       </c>
       <c r="H75">
         <v>2086.569</v>
@@ -5876,8 +6635,14 @@
       <c r="U75">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V75" t="s">
+        <v>269</v>
+      </c>
+      <c r="W75" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>9</v>
       </c>
@@ -5894,10 +6659,10 @@
         <v>3</v>
       </c>
       <c r="F76" t="s">
-        <v>169</v>
+        <v>271</v>
       </c>
       <c r="G76" t="s">
-        <v>170</v>
+        <v>272</v>
       </c>
       <c r="H76">
         <v>1740.5429999999999</v>
@@ -5940,6 +6705,12 @@
       </c>
       <c r="U76">
         <v>0</v>
+      </c>
+      <c r="V76" t="s">
+        <v>273</v>
+      </c>
+      <c r="W76" t="s">
+        <v>274</v>
       </c>
     </row>
   </sheetData>

--- a/datosSesiones.xlsx
+++ b/datosSesiones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\hlocal\C_TFG\Datos\Mision Colombia-20260209T150018Z-3-001\jsonToCsv_TFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{578773CA-B47C-4DE8-A49E-5714DF734B57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6444A42-89F9-40DA-B9C4-90BBEDE557A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="174">
   <si>
     <t>ID</t>
   </si>
@@ -110,72 +110,36 @@
     <t>15:20:46.000</t>
   </si>
   <si>
-    <t>78.57142857142857</t>
-  </si>
-  <si>
-    <t>21.42857142857143</t>
-  </si>
-  <si>
     <t>14:15:08.014</t>
   </si>
   <si>
     <t>14:41:36.785</t>
   </si>
   <si>
-    <t>88.23529411764706</t>
-  </si>
-  <si>
-    <t>11.764705882352942</t>
-  </si>
-  <si>
     <t>14:22:08.352</t>
   </si>
   <si>
     <t>14:45:59.368</t>
   </si>
   <si>
-    <t>84.61538461538461</t>
-  </si>
-  <si>
-    <t>15.384615384615387</t>
-  </si>
-  <si>
     <t>14:13:54.844</t>
   </si>
   <si>
     <t>14:29:18.332</t>
   </si>
   <si>
-    <t>84.21052631578948</t>
-  </si>
-  <si>
-    <t>15.78947368421052</t>
-  </si>
-  <si>
     <t>14:19:57.019</t>
   </si>
   <si>
     <t>14:33:28.259</t>
   </si>
   <si>
-    <t>88.88888888888889</t>
-  </si>
-  <si>
-    <t>11.111111111111114</t>
-  </si>
-  <si>
     <t>14:15:31.568</t>
   </si>
   <si>
     <t>14:40:03.212</t>
   </si>
   <si>
-    <t>95.0</t>
-  </si>
-  <si>
-    <t>5.0</t>
-  </si>
-  <si>
     <t>15:03:20.042</t>
   </si>
   <si>
@@ -191,108 +155,54 @@
     <t>15:55:50.529</t>
   </si>
   <si>
-    <t>62.5</t>
-  </si>
-  <si>
-    <t>37.5</t>
-  </si>
-  <si>
     <t>15:00:03.742</t>
   </si>
   <si>
     <t>15:36:46.952</t>
   </si>
   <si>
-    <t>95.23809523809524</t>
-  </si>
-  <si>
-    <t>4.761904761904759</t>
-  </si>
-  <si>
     <t>14:23:03.711</t>
   </si>
   <si>
     <t>14:47:23.112</t>
   </si>
   <si>
-    <t>92.85714285714286</t>
-  </si>
-  <si>
-    <t>7.142857142857139</t>
-  </si>
-  <si>
     <t>14:14:43.812</t>
   </si>
   <si>
     <t>14:44:49.452</t>
   </si>
   <si>
-    <t>93.75</t>
-  </si>
-  <si>
-    <t>6.25</t>
-  </si>
-  <si>
     <t>14:41:30.786</t>
   </si>
   <si>
     <t>14:55:21.747</t>
   </si>
   <si>
-    <t>76.47058823529412</t>
-  </si>
-  <si>
-    <t>23.529411764705884</t>
-  </si>
-  <si>
     <t>14:56:41.369</t>
   </si>
   <si>
     <t>15:12:14.966</t>
   </si>
   <si>
-    <t>86.66666666666667</t>
-  </si>
-  <si>
-    <t>13.333333333333329</t>
-  </si>
-  <si>
     <t>15:06:50.654</t>
   </si>
   <si>
     <t>15:43:52.114</t>
   </si>
   <si>
-    <t>83.33333333333333</t>
-  </si>
-  <si>
-    <t>16.66666666666667</t>
-  </si>
-  <si>
     <t>14:22:36.656</t>
   </si>
   <si>
     <t>14:50:51.188</t>
   </si>
   <si>
-    <t>81.25</t>
-  </si>
-  <si>
-    <t>18.75</t>
-  </si>
-  <si>
     <t>14:14:22.689</t>
   </si>
   <si>
     <t>14:32:03.553</t>
   </si>
   <si>
-    <t>92.5925925925926</t>
-  </si>
-  <si>
-    <t>7.407407407407405</t>
-  </si>
-  <si>
     <t>15:03:08.992</t>
   </si>
   <si>
@@ -305,48 +215,24 @@
     <t>15:51:25.871</t>
   </si>
   <si>
-    <t>90.3225806451613</t>
-  </si>
-  <si>
-    <t>9.677419354838705</t>
-  </si>
-  <si>
     <t>15:05:45.125</t>
   </si>
   <si>
     <t>15:51:06.619</t>
   </si>
   <si>
-    <t>90.9090909090909</t>
-  </si>
-  <si>
-    <t>9.090909090909093</t>
-  </si>
-  <si>
     <t>15:16:10.839</t>
   </si>
   <si>
     <t>15:43:29.980</t>
   </si>
   <si>
-    <t>94.73684210526316</t>
-  </si>
-  <si>
-    <t>5.263157894736835</t>
-  </si>
-  <si>
     <t>14:59:31.380</t>
   </si>
   <si>
     <t>15:53:03.221</t>
   </si>
   <si>
-    <t>88.63636363636364</t>
-  </si>
-  <si>
-    <t>11.36363636363636</t>
-  </si>
-  <si>
     <t>14:22:05.337</t>
   </si>
   <si>
@@ -359,21 +245,12 @@
     <t>15:29:19.230</t>
   </si>
   <si>
-    <t>50.0</t>
-  </si>
-  <si>
     <t>15:01:24.561</t>
   </si>
   <si>
     <t>15:51:01.360</t>
   </si>
   <si>
-    <t>76.74418604651163</t>
-  </si>
-  <si>
-    <t>23.25581395348837</t>
-  </si>
-  <si>
     <t>14:56:23.695</t>
   </si>
   <si>
@@ -386,48 +263,24 @@
     <t>15:42:14.394</t>
   </si>
   <si>
-    <t>87.5</t>
-  </si>
-  <si>
-    <t>12.5</t>
-  </si>
-  <si>
     <t>14:57:14.599</t>
   </si>
   <si>
     <t>15:25:56.336</t>
   </si>
   <si>
-    <t>100.0</t>
-  </si>
-  <si>
-    <t>0.0</t>
-  </si>
-  <si>
     <t>14:58:10.940</t>
   </si>
   <si>
     <t>15:40:59.178</t>
   </si>
   <si>
-    <t>75.0</t>
-  </si>
-  <si>
-    <t>25.0</t>
-  </si>
-  <si>
     <t>15:04:46.232</t>
   </si>
   <si>
     <t>15:20:10.657</t>
   </si>
   <si>
-    <t>60.0</t>
-  </si>
-  <si>
-    <t>40.0</t>
-  </si>
-  <si>
     <t>15:07:30.038</t>
   </si>
   <si>
@@ -446,72 +299,36 @@
     <t>15:29:11.613</t>
   </si>
   <si>
-    <t>78.94736842105263</t>
-  </si>
-  <si>
-    <t>21.05263157894737</t>
-  </si>
-  <si>
     <t>15:01:05.153</t>
   </si>
   <si>
     <t>15:42:28.525</t>
   </si>
   <si>
-    <t>76.78571428571429</t>
-  </si>
-  <si>
-    <t>23.214285714285708</t>
-  </si>
-  <si>
     <t>14:41:32.880</t>
   </si>
   <si>
     <t>15:11:40.452</t>
   </si>
   <si>
-    <t>92.3076923076923</t>
-  </si>
-  <si>
-    <t>7.692307692307693</t>
-  </si>
-  <si>
     <t>14:59:05.674</t>
   </si>
   <si>
     <t>15:53:16.524</t>
   </si>
   <si>
-    <t>83.78378378378379</t>
-  </si>
-  <si>
-    <t>16.21621621621621</t>
-  </si>
-  <si>
     <t>14:21:40.891</t>
   </si>
   <si>
     <t>14:53:52.881</t>
   </si>
   <si>
-    <t>90.2439024390244</t>
-  </si>
-  <si>
-    <t>9.756097560975604</t>
-  </si>
-  <si>
     <t>14:13:26.720</t>
   </si>
   <si>
     <t>14:26:27.789</t>
   </si>
   <si>
-    <t>90.47619047619048</t>
-  </si>
-  <si>
-    <t>9.523809523809518</t>
-  </si>
-  <si>
     <t>16:03:16.527</t>
   </si>
   <si>
@@ -536,36 +353,18 @@
     <t>16:44:13.973</t>
   </si>
   <si>
-    <t>83.87096774193549</t>
-  </si>
-  <si>
-    <t>16.129032258064512</t>
-  </si>
-  <si>
     <t>15:55:15.139</t>
   </si>
   <si>
     <t>16:28:02.631</t>
   </si>
   <si>
-    <t>80.76923076923077</t>
-  </si>
-  <si>
-    <t>19.230769230769226</t>
-  </si>
-  <si>
     <t>15:54:22.013</t>
   </si>
   <si>
     <t>16:20:28.972</t>
   </si>
   <si>
-    <t>96.42857142857143</t>
-  </si>
-  <si>
-    <t>3.5714285714285694</t>
-  </si>
-  <si>
     <t>15:03:42.632</t>
   </si>
   <si>
@@ -584,12 +383,6 @@
     <t>17:06:26.439</t>
   </si>
   <si>
-    <t>80.95238095238095</t>
-  </si>
-  <si>
-    <t>19.04761904761905</t>
-  </si>
-  <si>
     <t>15:04:10.151</t>
   </si>
   <si>
@@ -608,12 +401,6 @@
     <t>15:48:01.202</t>
   </si>
   <si>
-    <t>78.78787878787878</t>
-  </si>
-  <si>
-    <t>21.212121212121218</t>
-  </si>
-  <si>
     <t>15:41:43.127</t>
   </si>
   <si>
@@ -626,24 +413,12 @@
     <t>15:22:04.958</t>
   </si>
   <si>
-    <t>57.142857142857146</t>
-  </si>
-  <si>
-    <t>42.857142857142854</t>
-  </si>
-  <si>
     <t>14:53:45.380</t>
   </si>
   <si>
     <t>15:43:28.720</t>
   </si>
   <si>
-    <t>90.0</t>
-  </si>
-  <si>
-    <t>10.0</t>
-  </si>
-  <si>
     <t>15:22:11.114</t>
   </si>
   <si>
@@ -668,24 +443,12 @@
     <t>17:01:27.938</t>
   </si>
   <si>
-    <t>94.11764705882354</t>
-  </si>
-  <si>
-    <t>5.882352941176464</t>
-  </si>
-  <si>
     <t>14:14:16.150</t>
   </si>
   <si>
     <t>15:22:37.565</t>
   </si>
   <si>
-    <t>83.60655737704919</t>
-  </si>
-  <si>
-    <t>16.393442622950815</t>
-  </si>
-  <si>
     <t>16:50:34.650</t>
   </si>
   <si>
@@ -698,24 +461,12 @@
     <t>14:45:28.411</t>
   </si>
   <si>
-    <t>91.66666666666667</t>
-  </si>
-  <si>
-    <t>8.333333333333329</t>
-  </si>
-  <si>
     <t>14:14:40.795</t>
   </si>
   <si>
     <t>14:32:00.853</t>
   </si>
   <si>
-    <t>90.625</t>
-  </si>
-  <si>
-    <t>9.375</t>
-  </si>
-  <si>
     <t>14:21:08.325</t>
   </si>
   <si>
@@ -728,24 +479,12 @@
     <t>15:20:21.395</t>
   </si>
   <si>
-    <t>89.28571428571429</t>
-  </si>
-  <si>
-    <t>10.714285714285708</t>
-  </si>
-  <si>
     <t>14:20:39.906</t>
   </si>
   <si>
     <t>15:41:36.914</t>
   </si>
   <si>
-    <t>56.25</t>
-  </si>
-  <si>
-    <t>43.75</t>
-  </si>
-  <si>
     <t>15:41:05.914</t>
   </si>
   <si>
@@ -770,24 +509,12 @@
     <t>15:18:33.196</t>
   </si>
   <si>
-    <t>96.29629629629629</t>
-  </si>
-  <si>
-    <t>3.7037037037037095</t>
-  </si>
-  <si>
     <t>15:04:56.808</t>
   </si>
   <si>
     <t>15:20:16.102</t>
   </si>
   <si>
-    <t>66.66666666666667</t>
-  </si>
-  <si>
-    <t>33.33333333333333</t>
-  </si>
-  <si>
     <t>14:45:53.780</t>
   </si>
   <si>
@@ -800,12 +527,6 @@
     <t>14:42:45.564</t>
   </si>
   <si>
-    <t>75.86206896551724</t>
-  </si>
-  <si>
-    <t>24.13793103448276</t>
-  </si>
-  <si>
     <t>14:21:37.576</t>
   </si>
   <si>
@@ -818,46 +539,22 @@
     <t>14:59:25.079</t>
   </si>
   <si>
-    <t>71.42857142857143</t>
-  </si>
-  <si>
-    <t>28.57142857142857</t>
-  </si>
-  <si>
     <t>14:13:42.166</t>
   </si>
   <si>
     <t>14:58:20.061</t>
   </si>
   <si>
-    <t>76.0</t>
-  </si>
-  <si>
-    <t>24.0</t>
-  </si>
-  <si>
     <t>15:19:07.753</t>
   </si>
   <si>
     <t>15:53:54.322</t>
   </si>
   <si>
-    <t>91.30434782608695</t>
-  </si>
-  <si>
-    <t>8.695652173913047</t>
-  </si>
-  <si>
     <t>16:01:37.196</t>
   </si>
   <si>
     <t>16:30:37.739</t>
-  </si>
-  <si>
-    <t>77.14285714285714</t>
-  </si>
-  <si>
-    <t>22.85714285714286</t>
   </si>
 </sst>
 </file>
@@ -922,6 +619,20 @@
   </cellStyles>
   <dxfs count="3">
     <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -949,20 +660,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -977,7 +674,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A4099921-2F47-4780-A08B-0D05EB9D2D81}" name="Tabla1" displayName="Tabla1" ref="A1:W76" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A4099921-2F47-4780-A08B-0D05EB9D2D81}" name="Tabla1" displayName="Tabla1" ref="A1:W76" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
   <autoFilter ref="A1:W76" xr:uid="{A4099921-2F47-4780-A08B-0D05EB9D2D81}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{6576FD01-423D-418E-91CA-C5B75C6BBE93}" name="ID"/>
@@ -1452,11 +1149,11 @@
       <c r="U2">
         <v>0</v>
       </c>
-      <c r="V2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W2" t="s">
-        <v>26</v>
+      <c r="V2">
+        <v>78.571428571428498</v>
+      </c>
+      <c r="W2">
+        <v>21.428571428571399</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
@@ -1476,10 +1173,10 @@
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H3">
         <v>1588.771</v>
@@ -1523,11 +1220,11 @@
       <c r="U3">
         <v>2</v>
       </c>
-      <c r="V3" t="s">
-        <v>29</v>
-      </c>
-      <c r="W3" t="s">
-        <v>30</v>
+      <c r="V3">
+        <v>88.235294117647001</v>
+      </c>
+      <c r="W3">
+        <v>11.764705882352899</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.3">
@@ -1547,10 +1244,10 @@
         <v>4</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H4">
         <v>1431.0160000000001</v>
@@ -1594,11 +1291,11 @@
       <c r="U4">
         <v>1</v>
       </c>
-      <c r="V4" t="s">
-        <v>33</v>
-      </c>
-      <c r="W4" t="s">
-        <v>34</v>
+      <c r="V4">
+        <v>84.615384615384599</v>
+      </c>
+      <c r="W4">
+        <v>15.3846153846153</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.3">
@@ -1618,10 +1315,10 @@
         <v>3</v>
       </c>
       <c r="F5" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G5" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="H5">
         <v>923.48800000000006</v>
@@ -1665,11 +1362,11 @@
       <c r="U5">
         <v>0</v>
       </c>
-      <c r="V5" t="s">
-        <v>37</v>
-      </c>
-      <c r="W5" t="s">
-        <v>38</v>
+      <c r="V5">
+        <v>84.210526315789394</v>
+      </c>
+      <c r="W5">
+        <v>15.789473684210501</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.3">
@@ -1689,10 +1386,10 @@
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G6" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="H6">
         <v>811.24</v>
@@ -1736,11 +1433,11 @@
       <c r="U6">
         <v>1</v>
       </c>
-      <c r="V6" t="s">
-        <v>41</v>
-      </c>
-      <c r="W6" t="s">
-        <v>42</v>
+      <c r="V6">
+        <v>88.8888888888888</v>
+      </c>
+      <c r="W6">
+        <v>11.1111111111111</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.3">
@@ -1760,10 +1457,10 @@
         <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="G7" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="H7">
         <v>1471.644</v>
@@ -1807,11 +1504,11 @@
       <c r="U7">
         <v>1</v>
       </c>
-      <c r="V7" t="s">
-        <v>45</v>
-      </c>
-      <c r="W7" t="s">
-        <v>46</v>
+      <c r="V7">
+        <v>95</v>
+      </c>
+      <c r="W7">
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.3">
@@ -1831,10 +1528,10 @@
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H8">
         <v>1007.421</v>
@@ -1879,10 +1576,10 @@
         <v>2</v>
       </c>
       <c r="V8" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="W8" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.3">
@@ -1902,10 +1599,10 @@
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G9" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H9">
         <v>1568.1389999999999</v>
@@ -1949,11 +1646,11 @@
       <c r="U9">
         <v>2</v>
       </c>
-      <c r="V9" t="s">
-        <v>52</v>
-      </c>
-      <c r="W9" t="s">
-        <v>53</v>
+      <c r="V9">
+        <v>62.5</v>
+      </c>
+      <c r="W9">
+        <v>37.5</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.3">
@@ -1973,10 +1670,10 @@
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G10" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="H10">
         <v>2203.21</v>
@@ -2020,11 +1717,11 @@
       <c r="U10">
         <v>4</v>
       </c>
-      <c r="V10" t="s">
-        <v>56</v>
-      </c>
-      <c r="W10" t="s">
-        <v>57</v>
+      <c r="V10">
+        <v>95.238095238095198</v>
+      </c>
+      <c r="W10">
+        <v>4.7619047619047503</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.3">
@@ -2044,10 +1741,10 @@
         <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="G11" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="H11">
         <v>1459.4010000000001</v>
@@ -2091,11 +1788,11 @@
       <c r="U11">
         <v>0</v>
       </c>
-      <c r="V11" t="s">
-        <v>60</v>
-      </c>
-      <c r="W11" t="s">
-        <v>61</v>
+      <c r="V11">
+        <v>92.857142857142804</v>
+      </c>
+      <c r="W11">
+        <v>7.1428571428571299</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.3">
@@ -2115,10 +1812,10 @@
         <v>0</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="G12" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="H12">
         <v>1805.64</v>
@@ -2162,11 +1859,11 @@
       <c r="U12">
         <v>1</v>
       </c>
-      <c r="V12" t="s">
-        <v>64</v>
-      </c>
-      <c r="W12" t="s">
-        <v>65</v>
+      <c r="V12">
+        <v>93.75</v>
+      </c>
+      <c r="W12">
+        <v>6.25</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.3">
@@ -2186,10 +1883,10 @@
         <v>0</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="G13" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="H13">
         <v>830.96100000000001</v>
@@ -2233,11 +1930,11 @@
       <c r="U13">
         <v>0</v>
       </c>
-      <c r="V13" t="s">
-        <v>68</v>
-      </c>
-      <c r="W13" t="s">
-        <v>69</v>
+      <c r="V13">
+        <v>76.470588235294102</v>
+      </c>
+      <c r="W13">
+        <v>23.529411764705799</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.3">
@@ -2257,10 +1954,10 @@
         <v>3</v>
       </c>
       <c r="F14" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="G14" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="H14">
         <v>933.59699999999998</v>
@@ -2304,11 +2001,11 @@
       <c r="U14">
         <v>0</v>
       </c>
-      <c r="V14" t="s">
-        <v>72</v>
-      </c>
-      <c r="W14" t="s">
-        <v>73</v>
+      <c r="V14">
+        <v>86.6666666666666</v>
+      </c>
+      <c r="W14">
+        <v>13.3333333333333</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.3">
@@ -2328,10 +2025,10 @@
         <v>3</v>
       </c>
       <c r="F15" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="G15" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="H15">
         <v>2221.46</v>
@@ -2375,11 +2072,11 @@
       <c r="U15">
         <v>1</v>
       </c>
-      <c r="V15" t="s">
-        <v>76</v>
-      </c>
-      <c r="W15" t="s">
-        <v>77</v>
+      <c r="V15">
+        <v>83.3333333333333</v>
+      </c>
+      <c r="W15">
+        <v>16.6666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.3">
@@ -2399,10 +2096,10 @@
         <v>4</v>
       </c>
       <c r="F16" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="G16" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="H16">
         <v>1694.5319999999999</v>
@@ -2446,11 +2143,11 @@
       <c r="U16">
         <v>0</v>
       </c>
-      <c r="V16" t="s">
-        <v>80</v>
-      </c>
-      <c r="W16" t="s">
-        <v>81</v>
+      <c r="V16">
+        <v>81.25</v>
+      </c>
+      <c r="W16">
+        <v>18.75</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.3">
@@ -2470,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="F17" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="G17" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="H17">
         <v>1060.864</v>
@@ -2517,11 +2214,11 @@
       <c r="U17">
         <v>0</v>
       </c>
-      <c r="V17" t="s">
-        <v>84</v>
-      </c>
-      <c r="W17" t="s">
-        <v>85</v>
+      <c r="V17">
+        <v>92.592592592592595</v>
+      </c>
+      <c r="W17">
+        <v>7.4074074074074003</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.3">
@@ -2541,10 +2238,10 @@
         <v>0</v>
       </c>
       <c r="F18" t="s">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="G18" t="s">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="H18">
         <v>430.90499999999997</v>
@@ -2589,10 +2286,10 @@
         <v>0</v>
       </c>
       <c r="V18" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="W18" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.3">
@@ -2612,10 +2309,10 @@
         <v>0</v>
       </c>
       <c r="F19" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="G19" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="H19">
         <v>1570.5830000000001</v>
@@ -2659,11 +2356,11 @@
       <c r="U19">
         <v>0</v>
       </c>
-      <c r="V19" t="s">
-        <v>90</v>
-      </c>
-      <c r="W19" t="s">
-        <v>91</v>
+      <c r="V19">
+        <v>90.322580645161295</v>
+      </c>
+      <c r="W19">
+        <v>9.6774193548386993</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.3">
@@ -2683,10 +2380,10 @@
         <v>4</v>
       </c>
       <c r="F20" t="s">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="G20" t="s">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="H20">
         <v>2721.4940000000001</v>
@@ -2730,11 +2427,11 @@
       <c r="U20">
         <v>1</v>
       </c>
-      <c r="V20" t="s">
-        <v>94</v>
-      </c>
-      <c r="W20" t="s">
-        <v>95</v>
+      <c r="V20">
+        <v>90.909090909090907</v>
+      </c>
+      <c r="W20">
+        <v>9.0909090909090899</v>
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.3">
@@ -2754,10 +2451,10 @@
         <v>2</v>
       </c>
       <c r="F21" t="s">
-        <v>96</v>
+        <v>62</v>
       </c>
       <c r="G21" t="s">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="H21">
         <v>1639.1410000000001</v>
@@ -2801,11 +2498,11 @@
       <c r="U21">
         <v>0</v>
       </c>
-      <c r="V21" t="s">
-        <v>98</v>
-      </c>
-      <c r="W21" t="s">
-        <v>99</v>
+      <c r="V21">
+        <v>94.736842105263094</v>
+      </c>
+      <c r="W21">
+        <v>5.26315789473683</v>
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.3">
@@ -2825,10 +2522,10 @@
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="G22" t="s">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="H22">
         <v>3211.8409999999999</v>
@@ -2872,11 +2569,11 @@
       <c r="U22">
         <v>0</v>
       </c>
-      <c r="V22" t="s">
-        <v>102</v>
-      </c>
-      <c r="W22" t="s">
-        <v>103</v>
+      <c r="V22">
+        <v>88.636363636363598</v>
+      </c>
+      <c r="W22">
+        <v>11.363636363636299</v>
       </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.3">
@@ -2896,10 +2593,10 @@
         <v>0</v>
       </c>
       <c r="F23" t="s">
-        <v>104</v>
+        <v>66</v>
       </c>
       <c r="G23" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="H23">
         <v>1882.586</v>
@@ -2943,11 +2640,11 @@
       <c r="U23">
         <v>0</v>
       </c>
-      <c r="V23" t="s">
-        <v>25</v>
-      </c>
-      <c r="W23" t="s">
-        <v>26</v>
+      <c r="V23">
+        <v>78.571428571428498</v>
+      </c>
+      <c r="W23">
+        <v>21.428571428571399</v>
       </c>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.3">
@@ -2967,10 +2664,10 @@
         <v>0</v>
       </c>
       <c r="F24" t="s">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="G24" t="s">
-        <v>107</v>
+        <v>69</v>
       </c>
       <c r="H24">
         <v>1136.1980000000001</v>
@@ -3014,11 +2711,11 @@
       <c r="U24">
         <v>4</v>
       </c>
-      <c r="V24" t="s">
-        <v>108</v>
-      </c>
-      <c r="W24" t="s">
-        <v>108</v>
+      <c r="V24">
+        <v>50</v>
+      </c>
+      <c r="W24">
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.3">
@@ -3038,10 +2735,10 @@
         <v>2</v>
       </c>
       <c r="F25" t="s">
-        <v>109</v>
+        <v>70</v>
       </c>
       <c r="G25" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="H25">
         <v>2976.799</v>
@@ -3085,11 +2782,11 @@
       <c r="U25">
         <v>0</v>
       </c>
-      <c r="V25" t="s">
-        <v>111</v>
-      </c>
-      <c r="W25" t="s">
-        <v>112</v>
+      <c r="V25">
+        <v>76.744186046511601</v>
+      </c>
+      <c r="W25">
+        <v>23.2558139534883</v>
       </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.3">
@@ -3109,10 +2806,10 @@
         <v>0</v>
       </c>
       <c r="F26" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="G26" t="s">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="H26">
         <v>1595.1990000000001</v>
@@ -3156,11 +2853,11 @@
       <c r="U26">
         <v>1</v>
       </c>
-      <c r="V26" t="s">
-        <v>45</v>
-      </c>
-      <c r="W26" t="s">
-        <v>46</v>
+      <c r="V26">
+        <v>95</v>
+      </c>
+      <c r="W26">
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.3">
@@ -3180,10 +2877,10 @@
         <v>0</v>
       </c>
       <c r="F27" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="G27" t="s">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="H27">
         <v>2688.6970000000001</v>
@@ -3227,11 +2924,11 @@
       <c r="U27">
         <v>0</v>
       </c>
-      <c r="V27" t="s">
-        <v>117</v>
-      </c>
-      <c r="W27" t="s">
-        <v>118</v>
+      <c r="V27">
+        <v>87.5</v>
+      </c>
+      <c r="W27">
+        <v>12.5</v>
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.3">
@@ -3251,10 +2948,10 @@
         <v>0</v>
       </c>
       <c r="F28" t="s">
-        <v>119</v>
+        <v>76</v>
       </c>
       <c r="G28" t="s">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="H28">
         <v>1721.7370000000001</v>
@@ -3298,11 +2995,11 @@
       <c r="U28">
         <v>2</v>
       </c>
-      <c r="V28" t="s">
-        <v>121</v>
-      </c>
-      <c r="W28" t="s">
-        <v>122</v>
+      <c r="V28">
+        <v>100</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.3">
@@ -3322,10 +3019,10 @@
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>123</v>
+        <v>78</v>
       </c>
       <c r="G29" t="s">
-        <v>124</v>
+        <v>79</v>
       </c>
       <c r="H29">
         <v>2568.2379999999998</v>
@@ -3369,11 +3066,11 @@
       <c r="U29">
         <v>2</v>
       </c>
-      <c r="V29" t="s">
-        <v>125</v>
-      </c>
-      <c r="W29" t="s">
-        <v>126</v>
+      <c r="V29">
+        <v>75</v>
+      </c>
+      <c r="W29">
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.3">
@@ -3393,10 +3090,10 @@
         <v>0</v>
       </c>
       <c r="F30" t="s">
-        <v>127</v>
+        <v>80</v>
       </c>
       <c r="G30" t="s">
-        <v>128</v>
+        <v>81</v>
       </c>
       <c r="H30">
         <v>924.42499999999995</v>
@@ -3440,11 +3137,11 @@
       <c r="U30">
         <v>0</v>
       </c>
-      <c r="V30" t="s">
-        <v>129</v>
-      </c>
-      <c r="W30" t="s">
-        <v>130</v>
+      <c r="V30">
+        <v>60</v>
+      </c>
+      <c r="W30">
+        <v>40</v>
       </c>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.3">
@@ -3464,10 +3161,10 @@
         <v>0</v>
       </c>
       <c r="F31" t="s">
-        <v>131</v>
+        <v>82</v>
       </c>
       <c r="G31" t="s">
-        <v>132</v>
+        <v>83</v>
       </c>
       <c r="H31">
         <v>2739.4659999999999</v>
@@ -3511,11 +3208,11 @@
       <c r="U31">
         <v>3</v>
       </c>
-      <c r="V31" t="s">
-        <v>125</v>
-      </c>
-      <c r="W31" t="s">
-        <v>126</v>
+      <c r="V31">
+        <v>75</v>
+      </c>
+      <c r="W31">
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.3">
@@ -3535,10 +3232,10 @@
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>133</v>
+        <v>84</v>
       </c>
       <c r="G32" t="s">
-        <v>134</v>
+        <v>85</v>
       </c>
       <c r="H32">
         <v>2110.4520000000002</v>
@@ -3582,11 +3279,11 @@
       <c r="U32">
         <v>1</v>
       </c>
-      <c r="V32" t="s">
-        <v>117</v>
-      </c>
-      <c r="W32" t="s">
-        <v>118</v>
+      <c r="V32">
+        <v>87.5</v>
+      </c>
+      <c r="W32">
+        <v>12.5</v>
       </c>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.3">
@@ -3606,10 +3303,10 @@
         <v>3</v>
       </c>
       <c r="F33" t="s">
-        <v>135</v>
+        <v>86</v>
       </c>
       <c r="G33" t="s">
-        <v>136</v>
+        <v>87</v>
       </c>
       <c r="H33">
         <v>1783.269</v>
@@ -3653,11 +3350,11 @@
       <c r="U33">
         <v>0</v>
       </c>
-      <c r="V33" t="s">
-        <v>137</v>
-      </c>
-      <c r="W33" t="s">
-        <v>138</v>
+      <c r="V33">
+        <v>78.947368421052602</v>
+      </c>
+      <c r="W33">
+        <v>21.052631578947299</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.3">
@@ -3677,10 +3374,10 @@
         <v>4</v>
       </c>
       <c r="F34" t="s">
-        <v>139</v>
+        <v>88</v>
       </c>
       <c r="G34" t="s">
-        <v>140</v>
+        <v>89</v>
       </c>
       <c r="H34">
         <v>2483.3719999999998</v>
@@ -3724,11 +3421,11 @@
       <c r="U34">
         <v>2</v>
       </c>
-      <c r="V34" t="s">
-        <v>141</v>
-      </c>
-      <c r="W34" t="s">
-        <v>142</v>
+      <c r="V34">
+        <v>76.785714285714207</v>
+      </c>
+      <c r="W34">
+        <v>23.214285714285701</v>
       </c>
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.3">
@@ -3748,10 +3445,10 @@
         <v>0</v>
       </c>
       <c r="F35" t="s">
-        <v>143</v>
+        <v>90</v>
       </c>
       <c r="G35" t="s">
-        <v>144</v>
+        <v>91</v>
       </c>
       <c r="H35">
         <v>1807.5719999999999</v>
@@ -3795,11 +3492,11 @@
       <c r="U35">
         <v>3</v>
       </c>
-      <c r="V35" t="s">
-        <v>145</v>
-      </c>
-      <c r="W35" t="s">
-        <v>146</v>
+      <c r="V35">
+        <v>92.307692307692307</v>
+      </c>
+      <c r="W35">
+        <v>7.6923076923076898</v>
       </c>
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.3">
@@ -3819,10 +3516,10 @@
         <v>0</v>
       </c>
       <c r="F36" t="s">
-        <v>147</v>
+        <v>92</v>
       </c>
       <c r="G36" t="s">
-        <v>148</v>
+        <v>93</v>
       </c>
       <c r="H36">
         <v>3250.85</v>
@@ -3866,11 +3563,11 @@
       <c r="U36">
         <v>3</v>
       </c>
-      <c r="V36" t="s">
-        <v>149</v>
-      </c>
-      <c r="W36" t="s">
-        <v>150</v>
+      <c r="V36">
+        <v>83.783783783783704</v>
+      </c>
+      <c r="W36">
+        <v>16.2162162162162</v>
       </c>
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.3">
@@ -3890,10 +3587,10 @@
         <v>2</v>
       </c>
       <c r="F37" t="s">
-        <v>151</v>
+        <v>94</v>
       </c>
       <c r="G37" t="s">
-        <v>152</v>
+        <v>95</v>
       </c>
       <c r="H37">
         <v>1931.99</v>
@@ -3937,11 +3634,11 @@
       <c r="U37">
         <v>1</v>
       </c>
-      <c r="V37" t="s">
-        <v>153</v>
-      </c>
-      <c r="W37" t="s">
-        <v>154</v>
+      <c r="V37">
+        <v>90.243902439024396</v>
+      </c>
+      <c r="W37">
+        <v>9.7560975609756007</v>
       </c>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.3">
@@ -3961,10 +3658,10 @@
         <v>3</v>
       </c>
       <c r="F38" t="s">
-        <v>155</v>
+        <v>96</v>
       </c>
       <c r="G38" t="s">
-        <v>156</v>
+        <v>97</v>
       </c>
       <c r="H38">
         <v>781.06899999999996</v>
@@ -4008,11 +3705,11 @@
       <c r="U38">
         <v>0</v>
       </c>
-      <c r="V38" t="s">
-        <v>157</v>
-      </c>
-      <c r="W38" t="s">
-        <v>158</v>
+      <c r="V38">
+        <v>90.476190476190396</v>
+      </c>
+      <c r="W38">
+        <v>9.5238095238095095</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.3">
@@ -4032,10 +3729,10 @@
         <v>0</v>
       </c>
       <c r="F39" t="s">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="G39" t="s">
-        <v>160</v>
+        <v>99</v>
       </c>
       <c r="H39">
         <v>1462.616</v>
@@ -4080,10 +3777,10 @@
         <v>0</v>
       </c>
       <c r="V39" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="W39" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.3">
@@ -4103,10 +3800,10 @@
         <v>0</v>
       </c>
       <c r="F40" t="s">
-        <v>161</v>
+        <v>100</v>
       </c>
       <c r="G40" t="s">
-        <v>162</v>
+        <v>101</v>
       </c>
       <c r="H40">
         <v>1267.6220000000001</v>
@@ -4151,10 +3848,10 @@
         <v>0</v>
       </c>
       <c r="V40" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="W40" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.3">
@@ -4174,10 +3871,10 @@
         <v>0</v>
       </c>
       <c r="F41" t="s">
-        <v>163</v>
+        <v>102</v>
       </c>
       <c r="G41" t="s">
-        <v>164</v>
+        <v>103</v>
       </c>
       <c r="H41">
         <v>1885.146</v>
@@ -4222,10 +3919,10 @@
         <v>4</v>
       </c>
       <c r="V41" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="W41" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="42" spans="1:23" x14ac:dyDescent="0.3">
@@ -4245,10 +3942,10 @@
         <v>0</v>
       </c>
       <c r="F42" t="s">
-        <v>165</v>
+        <v>104</v>
       </c>
       <c r="G42" t="s">
-        <v>166</v>
+        <v>105</v>
       </c>
       <c r="H42">
         <v>3121.1120000000001</v>
@@ -4292,11 +3989,11 @@
       <c r="U42">
         <v>2</v>
       </c>
-      <c r="V42" t="s">
-        <v>167</v>
-      </c>
-      <c r="W42" t="s">
-        <v>168</v>
+      <c r="V42">
+        <v>83.870967741935402</v>
+      </c>
+      <c r="W42">
+        <v>16.129032258064498</v>
       </c>
     </row>
     <row r="43" spans="1:23" x14ac:dyDescent="0.3">
@@ -4316,10 +4013,10 @@
         <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>169</v>
+        <v>106</v>
       </c>
       <c r="G43" t="s">
-        <v>170</v>
+        <v>107</v>
       </c>
       <c r="H43">
         <v>1967.492</v>
@@ -4363,11 +4060,11 @@
       <c r="U43">
         <v>1</v>
       </c>
-      <c r="V43" t="s">
-        <v>171</v>
-      </c>
-      <c r="W43" t="s">
-        <v>172</v>
+      <c r="V43">
+        <v>80.769230769230703</v>
+      </c>
+      <c r="W43">
+        <v>19.230769230769202</v>
       </c>
     </row>
     <row r="44" spans="1:23" x14ac:dyDescent="0.3">
@@ -4387,10 +4084,10 @@
         <v>1</v>
       </c>
       <c r="F44" t="s">
-        <v>173</v>
+        <v>108</v>
       </c>
       <c r="G44" t="s">
-        <v>174</v>
+        <v>109</v>
       </c>
       <c r="H44">
         <v>1566.9590000000001</v>
@@ -4434,11 +4131,11 @@
       <c r="U44">
         <v>2</v>
       </c>
-      <c r="V44" t="s">
-        <v>175</v>
-      </c>
-      <c r="W44" t="s">
-        <v>176</v>
+      <c r="V44">
+        <v>96.428571428571402</v>
+      </c>
+      <c r="W44">
+        <v>3.5714285714285601</v>
       </c>
     </row>
     <row r="45" spans="1:23" x14ac:dyDescent="0.3">
@@ -4458,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="F45" t="s">
-        <v>177</v>
+        <v>110</v>
       </c>
       <c r="G45" t="s">
-        <v>178</v>
+        <v>111</v>
       </c>
       <c r="H45">
         <v>7.0000000000000001E-3</v>
@@ -4506,10 +4203,10 @@
         <v>0</v>
       </c>
       <c r="V45" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="W45" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.3">
@@ -4529,10 +4226,10 @@
         <v>0</v>
       </c>
       <c r="F46" t="s">
-        <v>179</v>
+        <v>112</v>
       </c>
       <c r="G46" t="s">
-        <v>180</v>
+        <v>113</v>
       </c>
       <c r="H46">
         <v>379.57600000000002</v>
@@ -4577,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="V46" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="W46" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="47" spans="1:23" x14ac:dyDescent="0.3">
@@ -4600,10 +4297,10 @@
         <v>1</v>
       </c>
       <c r="F47" t="s">
-        <v>181</v>
+        <v>114</v>
       </c>
       <c r="G47" t="s">
-        <v>182</v>
+        <v>115</v>
       </c>
       <c r="H47">
         <v>1186.057</v>
@@ -4647,11 +4344,11 @@
       <c r="U47">
         <v>1</v>
       </c>
-      <c r="V47" t="s">
-        <v>183</v>
-      </c>
-      <c r="W47" t="s">
-        <v>184</v>
+      <c r="V47">
+        <v>80.952380952380906</v>
+      </c>
+      <c r="W47">
+        <v>19.047619047619001</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.3">
@@ -4671,10 +4368,10 @@
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>185</v>
+        <v>116</v>
       </c>
       <c r="G48" t="s">
-        <v>186</v>
+        <v>117</v>
       </c>
       <c r="H48">
         <v>1128.722</v>
@@ -4719,10 +4416,10 @@
         <v>2</v>
       </c>
       <c r="V48" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="W48" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="49" spans="1:23" x14ac:dyDescent="0.3">
@@ -4742,10 +4439,10 @@
         <v>0</v>
       </c>
       <c r="F49" t="s">
-        <v>187</v>
+        <v>118</v>
       </c>
       <c r="G49" t="s">
-        <v>188</v>
+        <v>119</v>
       </c>
       <c r="H49">
         <v>1324.854</v>
@@ -4789,11 +4486,11 @@
       <c r="U49">
         <v>0</v>
       </c>
-      <c r="V49" t="s">
-        <v>41</v>
-      </c>
-      <c r="W49" t="s">
-        <v>42</v>
+      <c r="V49">
+        <v>88.8888888888888</v>
+      </c>
+      <c r="W49">
+        <v>11.1111111111111</v>
       </c>
     </row>
     <row r="50" spans="1:23" x14ac:dyDescent="0.3">
@@ -4813,10 +4510,10 @@
         <v>1</v>
       </c>
       <c r="F50" t="s">
-        <v>189</v>
+        <v>120</v>
       </c>
       <c r="G50" t="s">
-        <v>190</v>
+        <v>121</v>
       </c>
       <c r="H50">
         <v>1245.463</v>
@@ -4860,11 +4557,11 @@
       <c r="U50">
         <v>2</v>
       </c>
-      <c r="V50" t="s">
-        <v>191</v>
-      </c>
-      <c r="W50" t="s">
-        <v>192</v>
+      <c r="V50">
+        <v>78.787878787878697</v>
+      </c>
+      <c r="W50">
+        <v>21.2121212121212</v>
       </c>
     </row>
     <row r="51" spans="1:23" x14ac:dyDescent="0.3">
@@ -4884,10 +4581,10 @@
         <v>0</v>
       </c>
       <c r="F51" t="s">
-        <v>193</v>
+        <v>122</v>
       </c>
       <c r="G51" t="s">
-        <v>194</v>
+        <v>123</v>
       </c>
       <c r="H51">
         <v>744.75</v>
@@ -4932,10 +4629,10 @@
         <v>1</v>
       </c>
       <c r="V51" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="W51" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="52" spans="1:23" x14ac:dyDescent="0.3">
@@ -4955,10 +4652,10 @@
         <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>195</v>
+        <v>124</v>
       </c>
       <c r="G52" t="s">
-        <v>196</v>
+        <v>125</v>
       </c>
       <c r="H52">
         <v>1124.6210000000001</v>
@@ -5002,11 +4699,11 @@
       <c r="U52">
         <v>5</v>
       </c>
-      <c r="V52" t="s">
-        <v>197</v>
-      </c>
-      <c r="W52" t="s">
-        <v>198</v>
+      <c r="V52">
+        <v>57.142857142857103</v>
+      </c>
+      <c r="W52">
+        <v>42.857142857142797</v>
       </c>
     </row>
     <row r="53" spans="1:23" x14ac:dyDescent="0.3">
@@ -5026,10 +4723,10 @@
         <v>3</v>
       </c>
       <c r="F53" t="s">
-        <v>199</v>
+        <v>126</v>
       </c>
       <c r="G53" t="s">
-        <v>200</v>
+        <v>127</v>
       </c>
       <c r="H53">
         <v>2983.34</v>
@@ -5073,11 +4770,11 @@
       <c r="U53">
         <v>6</v>
       </c>
-      <c r="V53" t="s">
-        <v>201</v>
-      </c>
-      <c r="W53" t="s">
-        <v>202</v>
+      <c r="V53">
+        <v>90</v>
+      </c>
+      <c r="W53">
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:23" x14ac:dyDescent="0.3">
@@ -5097,10 +4794,10 @@
         <v>0</v>
       </c>
       <c r="F54" t="s">
-        <v>203</v>
+        <v>128</v>
       </c>
       <c r="G54" t="s">
-        <v>204</v>
+        <v>129</v>
       </c>
       <c r="H54">
         <v>791.346</v>
@@ -5144,11 +4841,11 @@
       <c r="U54">
         <v>2</v>
       </c>
-      <c r="V54" t="s">
-        <v>125</v>
-      </c>
-      <c r="W54" t="s">
-        <v>126</v>
+      <c r="V54">
+        <v>75</v>
+      </c>
+      <c r="W54">
+        <v>25</v>
       </c>
     </row>
     <row r="55" spans="1:23" x14ac:dyDescent="0.3">
@@ -5168,10 +4865,10 @@
         <v>0</v>
       </c>
       <c r="F55" t="s">
-        <v>205</v>
+        <v>130</v>
       </c>
       <c r="G55" t="s">
-        <v>206</v>
+        <v>131</v>
       </c>
       <c r="H55">
         <v>302.63299999999998</v>
@@ -5215,11 +4912,11 @@
       <c r="U55">
         <v>0</v>
       </c>
-      <c r="V55" t="s">
-        <v>121</v>
-      </c>
-      <c r="W55" t="s">
-        <v>122</v>
+      <c r="V55">
+        <v>100</v>
+      </c>
+      <c r="W55">
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:23" x14ac:dyDescent="0.3">
@@ -5239,10 +4936,10 @@
         <v>1</v>
       </c>
       <c r="F56" t="s">
-        <v>207</v>
+        <v>132</v>
       </c>
       <c r="G56" t="s">
-        <v>208</v>
+        <v>133</v>
       </c>
       <c r="H56">
         <v>3785.3609999999999</v>
@@ -5286,11 +4983,11 @@
       <c r="U56">
         <v>7</v>
       </c>
-      <c r="V56" t="s">
-        <v>108</v>
-      </c>
-      <c r="W56" t="s">
-        <v>108</v>
+      <c r="V56">
+        <v>50</v>
+      </c>
+      <c r="W56">
+        <v>50</v>
       </c>
     </row>
     <row r="57" spans="1:23" x14ac:dyDescent="0.3">
@@ -5310,10 +5007,10 @@
         <v>1</v>
       </c>
       <c r="F57" t="s">
-        <v>209</v>
+        <v>134</v>
       </c>
       <c r="G57" t="s">
-        <v>210</v>
+        <v>135</v>
       </c>
       <c r="H57">
         <v>2002.558</v>
@@ -5357,11 +5054,11 @@
       <c r="U57">
         <v>2</v>
       </c>
-      <c r="V57" t="s">
-        <v>211</v>
-      </c>
-      <c r="W57" t="s">
-        <v>212</v>
+      <c r="V57">
+        <v>94.117647058823493</v>
+      </c>
+      <c r="W57">
+        <v>5.8823529411764603</v>
       </c>
     </row>
     <row r="58" spans="1:23" x14ac:dyDescent="0.3">
@@ -5381,10 +5078,10 @@
         <v>1</v>
       </c>
       <c r="F58" t="s">
-        <v>213</v>
+        <v>136</v>
       </c>
       <c r="G58" t="s">
-        <v>214</v>
+        <v>137</v>
       </c>
       <c r="H58">
         <v>4101.415</v>
@@ -5428,11 +5125,11 @@
       <c r="U58">
         <v>0</v>
       </c>
-      <c r="V58" t="s">
-        <v>215</v>
-      </c>
-      <c r="W58" t="s">
-        <v>216</v>
+      <c r="V58">
+        <v>83.6065573770491</v>
+      </c>
+      <c r="W58">
+        <v>16.393442622950801</v>
       </c>
     </row>
     <row r="59" spans="1:23" x14ac:dyDescent="0.3">
@@ -5452,10 +5149,10 @@
         <v>1</v>
       </c>
       <c r="F59" t="s">
-        <v>217</v>
+        <v>138</v>
       </c>
       <c r="G59" t="s">
-        <v>218</v>
+        <v>139</v>
       </c>
       <c r="H59">
         <v>1904.759</v>
@@ -5499,11 +5196,11 @@
       <c r="U59">
         <v>0</v>
       </c>
-      <c r="V59" t="s">
-        <v>197</v>
-      </c>
-      <c r="W59" t="s">
-        <v>198</v>
+      <c r="V59">
+        <v>57.142857142857103</v>
+      </c>
+      <c r="W59">
+        <v>42.857142857142797</v>
       </c>
     </row>
     <row r="60" spans="1:23" x14ac:dyDescent="0.3">
@@ -5523,10 +5220,10 @@
         <v>4</v>
       </c>
       <c r="F60" t="s">
-        <v>219</v>
+        <v>140</v>
       </c>
       <c r="G60" t="s">
-        <v>220</v>
+        <v>141</v>
       </c>
       <c r="H60">
         <v>1371.93</v>
@@ -5570,11 +5267,11 @@
       <c r="U60">
         <v>0</v>
       </c>
-      <c r="V60" t="s">
-        <v>221</v>
-      </c>
-      <c r="W60" t="s">
-        <v>222</v>
+      <c r="V60">
+        <v>91.6666666666666</v>
+      </c>
+      <c r="W60">
+        <v>8.3333333333333197</v>
       </c>
     </row>
     <row r="61" spans="1:23" x14ac:dyDescent="0.3">
@@ -5594,10 +5291,10 @@
         <v>3</v>
       </c>
       <c r="F61" t="s">
-        <v>223</v>
+        <v>142</v>
       </c>
       <c r="G61" t="s">
-        <v>224</v>
+        <v>143</v>
       </c>
       <c r="H61">
         <v>1040.058</v>
@@ -5641,11 +5338,11 @@
       <c r="U61">
         <v>1</v>
       </c>
-      <c r="V61" t="s">
-        <v>225</v>
-      </c>
-      <c r="W61" t="s">
-        <v>226</v>
+      <c r="V61">
+        <v>90.625</v>
+      </c>
+      <c r="W61">
+        <v>9.375</v>
       </c>
     </row>
     <row r="62" spans="1:23" x14ac:dyDescent="0.3">
@@ -5665,10 +5362,10 @@
         <v>0</v>
       </c>
       <c r="F62" t="s">
-        <v>227</v>
+        <v>144</v>
       </c>
       <c r="G62" t="s">
-        <v>228</v>
+        <v>145</v>
       </c>
       <c r="H62">
         <v>1945.4490000000001</v>
@@ -5712,11 +5409,11 @@
       <c r="U62">
         <v>0</v>
       </c>
-      <c r="V62" t="s">
-        <v>72</v>
-      </c>
-      <c r="W62" t="s">
-        <v>73</v>
+      <c r="V62">
+        <v>86.6666666666666</v>
+      </c>
+      <c r="W62">
+        <v>13.3333333333333</v>
       </c>
     </row>
     <row r="63" spans="1:23" x14ac:dyDescent="0.3">
@@ -5736,10 +5433,10 @@
         <v>3</v>
       </c>
       <c r="F63" t="s">
-        <v>229</v>
+        <v>146</v>
       </c>
       <c r="G63" t="s">
-        <v>230</v>
+        <v>147</v>
       </c>
       <c r="H63">
         <v>2758.1469999999999</v>
@@ -5783,11 +5480,11 @@
       <c r="U63">
         <v>0</v>
       </c>
-      <c r="V63" t="s">
-        <v>231</v>
-      </c>
-      <c r="W63" t="s">
-        <v>232</v>
+      <c r="V63">
+        <v>89.285714285714207</v>
+      </c>
+      <c r="W63">
+        <v>10.714285714285699</v>
       </c>
     </row>
     <row r="64" spans="1:23" x14ac:dyDescent="0.3">
@@ -5807,10 +5504,10 @@
         <v>0</v>
       </c>
       <c r="F64" t="s">
-        <v>233</v>
+        <v>148</v>
       </c>
       <c r="G64" t="s">
-        <v>234</v>
+        <v>149</v>
       </c>
       <c r="H64">
         <v>4857.0079999999998</v>
@@ -5854,11 +5551,11 @@
       <c r="U64">
         <v>3</v>
       </c>
-      <c r="V64" t="s">
-        <v>235</v>
-      </c>
-      <c r="W64" t="s">
-        <v>236</v>
+      <c r="V64">
+        <v>56.25</v>
+      </c>
+      <c r="W64">
+        <v>43.75</v>
       </c>
     </row>
     <row r="65" spans="1:23" x14ac:dyDescent="0.3">
@@ -5878,10 +5575,10 @@
         <v>1</v>
       </c>
       <c r="F65" t="s">
-        <v>237</v>
+        <v>150</v>
       </c>
       <c r="G65" t="s">
-        <v>238</v>
+        <v>151</v>
       </c>
       <c r="H65">
         <v>136.624</v>
@@ -5925,11 +5622,11 @@
       <c r="U65">
         <v>0</v>
       </c>
-      <c r="V65" t="s">
-        <v>121</v>
-      </c>
-      <c r="W65" t="s">
-        <v>122</v>
+      <c r="V65">
+        <v>100</v>
+      </c>
+      <c r="W65">
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:23" x14ac:dyDescent="0.3">
@@ -5949,10 +5646,10 @@
         <v>0</v>
       </c>
       <c r="F66" t="s">
-        <v>239</v>
+        <v>152</v>
       </c>
       <c r="G66" t="s">
-        <v>240</v>
+        <v>153</v>
       </c>
       <c r="H66">
         <v>1212.942</v>
@@ -5996,11 +5693,11 @@
       <c r="U66">
         <v>0</v>
       </c>
-      <c r="V66" t="s">
-        <v>125</v>
-      </c>
-      <c r="W66" t="s">
-        <v>126</v>
+      <c r="V66">
+        <v>75</v>
+      </c>
+      <c r="W66">
+        <v>25</v>
       </c>
     </row>
     <row r="67" spans="1:23" x14ac:dyDescent="0.3">
@@ -6020,10 +5717,10 @@
         <v>2</v>
       </c>
       <c r="F67" t="s">
-        <v>241</v>
+        <v>154</v>
       </c>
       <c r="G67" t="s">
-        <v>242</v>
+        <v>155</v>
       </c>
       <c r="H67">
         <v>585.04700000000003</v>
@@ -6067,11 +5764,11 @@
       <c r="U67">
         <v>1</v>
       </c>
-      <c r="V67" t="s">
-        <v>145</v>
-      </c>
-      <c r="W67" t="s">
-        <v>146</v>
+      <c r="V67">
+        <v>92.307692307692307</v>
+      </c>
+      <c r="W67">
+        <v>7.6923076923076898</v>
       </c>
     </row>
     <row r="68" spans="1:23" x14ac:dyDescent="0.3">
@@ -6091,10 +5788,10 @@
         <v>3</v>
       </c>
       <c r="F68" t="s">
-        <v>243</v>
+        <v>156</v>
       </c>
       <c r="G68" t="s">
-        <v>244</v>
+        <v>157</v>
       </c>
       <c r="H68">
         <v>1203.318</v>
@@ -6138,11 +5835,11 @@
       <c r="U68">
         <v>0</v>
       </c>
-      <c r="V68" t="s">
-        <v>245</v>
-      </c>
-      <c r="W68" t="s">
-        <v>246</v>
+      <c r="V68">
+        <v>96.296296296296205</v>
+      </c>
+      <c r="W68">
+        <v>3.7037037037037002</v>
       </c>
     </row>
     <row r="69" spans="1:23" x14ac:dyDescent="0.3">
@@ -6162,10 +5859,10 @@
         <v>0</v>
       </c>
       <c r="F69" t="s">
-        <v>247</v>
+        <v>158</v>
       </c>
       <c r="G69" t="s">
-        <v>248</v>
+        <v>159</v>
       </c>
       <c r="H69">
         <v>919.29399999999998</v>
@@ -6209,11 +5906,11 @@
       <c r="U69">
         <v>1</v>
       </c>
-      <c r="V69" t="s">
-        <v>249</v>
-      </c>
-      <c r="W69" t="s">
-        <v>250</v>
+      <c r="V69">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="W69">
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="70" spans="1:23" x14ac:dyDescent="0.3">
@@ -6233,10 +5930,10 @@
         <v>0</v>
       </c>
       <c r="F70" t="s">
-        <v>251</v>
+        <v>160</v>
       </c>
       <c r="G70" t="s">
-        <v>252</v>
+        <v>161</v>
       </c>
       <c r="H70">
         <v>33.176000000000002</v>
@@ -6281,10 +5978,10 @@
         <v>0</v>
       </c>
       <c r="V70" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="W70" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="71" spans="1:23" x14ac:dyDescent="0.3">
@@ -6304,10 +6001,10 @@
         <v>0</v>
       </c>
       <c r="F71" t="s">
-        <v>253</v>
+        <v>162</v>
       </c>
       <c r="G71" t="s">
-        <v>254</v>
+        <v>163</v>
       </c>
       <c r="H71">
         <v>1650.8009999999999</v>
@@ -6351,11 +6048,11 @@
       <c r="U71">
         <v>0</v>
       </c>
-      <c r="V71" t="s">
-        <v>255</v>
-      </c>
-      <c r="W71" t="s">
-        <v>256</v>
+      <c r="V71">
+        <v>75.862068965517196</v>
+      </c>
+      <c r="W71">
+        <v>24.137931034482701</v>
       </c>
     </row>
     <row r="72" spans="1:23" x14ac:dyDescent="0.3">
@@ -6375,10 +6072,10 @@
         <v>0</v>
       </c>
       <c r="F72" t="s">
-        <v>257</v>
+        <v>164</v>
       </c>
       <c r="G72" t="s">
-        <v>258</v>
+        <v>165</v>
       </c>
       <c r="H72">
         <v>979.68100000000004</v>
@@ -6423,10 +6120,10 @@
         <v>0</v>
       </c>
       <c r="V72" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="W72" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="73" spans="1:23" x14ac:dyDescent="0.3">
@@ -6446,10 +6143,10 @@
         <v>0</v>
       </c>
       <c r="F73" t="s">
-        <v>259</v>
+        <v>166</v>
       </c>
       <c r="G73" t="s">
-        <v>260</v>
+        <v>167</v>
       </c>
       <c r="H73">
         <v>1146.846</v>
@@ -6493,11 +6190,11 @@
       <c r="U73">
         <v>0</v>
       </c>
-      <c r="V73" t="s">
-        <v>261</v>
-      </c>
-      <c r="W73" t="s">
-        <v>262</v>
+      <c r="V73">
+        <v>71.428571428571402</v>
+      </c>
+      <c r="W73">
+        <v>28.571428571428498</v>
       </c>
     </row>
     <row r="74" spans="1:23" x14ac:dyDescent="0.3">
@@ -6517,10 +6214,10 @@
         <v>0</v>
       </c>
       <c r="F74" t="s">
-        <v>263</v>
+        <v>168</v>
       </c>
       <c r="G74" t="s">
-        <v>264</v>
+        <v>169</v>
       </c>
       <c r="H74">
         <v>2677.895</v>
@@ -6564,11 +6261,11 @@
       <c r="U74">
         <v>2</v>
       </c>
-      <c r="V74" t="s">
-        <v>265</v>
-      </c>
-      <c r="W74" t="s">
-        <v>266</v>
+      <c r="V74">
+        <v>76</v>
+      </c>
+      <c r="W74">
+        <v>24</v>
       </c>
     </row>
     <row r="75" spans="1:23" x14ac:dyDescent="0.3">
@@ -6588,10 +6285,10 @@
         <v>4</v>
       </c>
       <c r="F75" t="s">
-        <v>267</v>
+        <v>170</v>
       </c>
       <c r="G75" t="s">
-        <v>268</v>
+        <v>171</v>
       </c>
       <c r="H75">
         <v>2086.569</v>
@@ -6635,11 +6332,11 @@
       <c r="U75">
         <v>0</v>
       </c>
-      <c r="V75" t="s">
-        <v>269</v>
-      </c>
-      <c r="W75" t="s">
-        <v>270</v>
+      <c r="V75">
+        <v>91.304347826086897</v>
+      </c>
+      <c r="W75">
+        <v>8.6956521739130395</v>
       </c>
     </row>
     <row r="76" spans="1:23" x14ac:dyDescent="0.3">
@@ -6659,10 +6356,10 @@
         <v>3</v>
       </c>
       <c r="F76" t="s">
-        <v>271</v>
+        <v>172</v>
       </c>
       <c r="G76" t="s">
-        <v>272</v>
+        <v>173</v>
       </c>
       <c r="H76">
         <v>1740.5429999999999</v>
@@ -6706,11 +6403,11 @@
       <c r="U76">
         <v>0</v>
       </c>
-      <c r="V76" t="s">
-        <v>273</v>
-      </c>
-      <c r="W76" t="s">
-        <v>274</v>
+      <c r="V76">
+        <v>77.142857142857096</v>
+      </c>
+      <c r="W76">
+        <v>22.857142857142801</v>
       </c>
     </row>
   </sheetData>
